--- a/TRACK_MONITORING_REPORT.xlsx
+++ b/TRACK_MONITORING_REPORT.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMP" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="mm\-dd\-yy"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -100,6 +101,13 @@
       <sz val="20"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -115,7 +123,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -258,11 +266,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -357,6 +371,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3764,4 +3783,83 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="44" t="inlineStr">
+        <is>
+          <t>ROAD MOUNTABLE PRISM (RMP) MONITORING</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="45" t="inlineStr">
+        <is>
+          <t>Point Name</t>
+        </is>
+      </c>
+      <c r="C3" s="45" t="inlineStr">
+        <is>
+          <t>Delta Northing (DN)</t>
+        </is>
+      </c>
+      <c r="D3" s="45" t="inlineStr">
+        <is>
+          <t>Delta Easting (DE)</t>
+        </is>
+      </c>
+      <c r="E3" s="45" t="inlineStr">
+        <is>
+          <t>Delta Elevation (DELV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="46" t="inlineStr">
+        <is>
+          <t>RMP-A</t>
+        </is>
+      </c>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="46" t="inlineStr">
+        <is>
+          <t>RMP-B</t>
+        </is>
+      </c>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="46" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="46" t="inlineStr">
+        <is>
+          <t>RMP-C</t>
+        </is>
+      </c>
+      <c r="C6" s="46" t="n"/>
+      <c r="D6" s="46" t="n"/>
+      <c r="E6" s="46" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/TRACK_MONITORING_REPORT.xlsx
+++ b/TRACK_MONITORING_REPORT.xlsx
@@ -16,9 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="mm\-dd\-yy"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -276,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -376,6 +377,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1060,17 +1063,17 @@
       <c r="B15" s="32" t="n">
         <v>100</v>
       </c>
-      <c r="C15" s="33" t="n"/>
-      <c r="D15" s="33" t="n"/>
-      <c r="E15" s="33" t="n"/>
+      <c r="C15" s="47" t="n"/>
+      <c r="D15" s="47" t="n"/>
+      <c r="E15" s="47" t="n"/>
       <c r="F15" s="32">
         <f>B15+1</f>
         <v/>
       </c>
-      <c r="G15" s="33" t="n"/>
-      <c r="H15" s="33" t="n"/>
-      <c r="I15" s="33" t="n"/>
-      <c r="J15" s="33">
+      <c r="G15" s="47" t="n"/>
+      <c r="H15" s="47" t="n"/>
+      <c r="I15" s="47" t="n"/>
+      <c r="J15" s="47">
         <f>IF(OR(NOT(ISNUMBER(E15)),NOT(ISNUMBER(I15))),"NULL",E15-I15)</f>
         <v/>
       </c>
@@ -1082,17 +1085,17 @@
         <f>B15+2</f>
         <v/>
       </c>
-      <c r="C16" s="33" t="n"/>
-      <c r="D16" s="33" t="n"/>
-      <c r="E16" s="33" t="n"/>
+      <c r="C16" s="47" t="n"/>
+      <c r="D16" s="47" t="n"/>
+      <c r="E16" s="47" t="n"/>
       <c r="F16" s="32">
         <f>F15+2</f>
         <v/>
       </c>
-      <c r="G16" s="33" t="n"/>
-      <c r="H16" s="33" t="n"/>
-      <c r="I16" s="33" t="n"/>
-      <c r="J16" s="33">
+      <c r="G16" s="47" t="n"/>
+      <c r="H16" s="47" t="n"/>
+      <c r="I16" s="47" t="n"/>
+      <c r="J16" s="47">
         <f>IF(OR(NOT(ISNUMBER(E16)),NOT(ISNUMBER(I16))),"NULL",E16-I16)</f>
         <v/>
       </c>
@@ -1104,17 +1107,17 @@
         <f>B16+2</f>
         <v/>
       </c>
-      <c r="C17" s="33" t="n"/>
-      <c r="D17" s="33" t="n"/>
-      <c r="E17" s="33" t="n"/>
+      <c r="C17" s="47" t="n"/>
+      <c r="D17" s="47" t="n"/>
+      <c r="E17" s="47" t="n"/>
       <c r="F17" s="32">
         <f>F16+2</f>
         <v/>
       </c>
-      <c r="G17" s="33" t="n"/>
-      <c r="H17" s="33" t="n"/>
-      <c r="I17" s="33" t="n"/>
-      <c r="J17" s="33">
+      <c r="G17" s="47" t="n"/>
+      <c r="H17" s="47" t="n"/>
+      <c r="I17" s="47" t="n"/>
+      <c r="J17" s="47">
         <f>IF(OR(NOT(ISNUMBER(E17)),NOT(ISNUMBER(I17))),"NULL",E17-I17)</f>
         <v/>
       </c>
@@ -1126,17 +1129,17 @@
         <f>B17+2</f>
         <v/>
       </c>
-      <c r="C18" s="33" t="n"/>
-      <c r="D18" s="33" t="n"/>
-      <c r="E18" s="33" t="n"/>
+      <c r="C18" s="47" t="n"/>
+      <c r="D18" s="47" t="n"/>
+      <c r="E18" s="47" t="n"/>
       <c r="F18" s="32">
         <f>F17+2</f>
         <v/>
       </c>
-      <c r="G18" s="33" t="n"/>
-      <c r="H18" s="33" t="n"/>
-      <c r="I18" s="33" t="n"/>
-      <c r="J18" s="33">
+      <c r="G18" s="47" t="n"/>
+      <c r="H18" s="47" t="n"/>
+      <c r="I18" s="47" t="n"/>
+      <c r="J18" s="47">
         <f>IF(OR(NOT(ISNUMBER(E18)),NOT(ISNUMBER(I18))),"NULL",E18-I18)</f>
         <v/>
       </c>
@@ -1148,17 +1151,17 @@
         <f>B18+2</f>
         <v/>
       </c>
-      <c r="C19" s="33" t="n"/>
-      <c r="D19" s="33" t="n"/>
-      <c r="E19" s="33" t="n"/>
+      <c r="C19" s="47" t="n"/>
+      <c r="D19" s="47" t="n"/>
+      <c r="E19" s="47" t="n"/>
       <c r="F19" s="32">
         <f>F18+2</f>
         <v/>
       </c>
-      <c r="G19" s="33" t="n"/>
-      <c r="H19" s="33" t="n"/>
-      <c r="I19" s="33" t="n"/>
-      <c r="J19" s="33">
+      <c r="G19" s="47" t="n"/>
+      <c r="H19" s="47" t="n"/>
+      <c r="I19" s="47" t="n"/>
+      <c r="J19" s="47">
         <f>IF(OR(NOT(ISNUMBER(E19)),NOT(ISNUMBER(I19))),"NULL",E19-I19)</f>
         <v/>
       </c>
@@ -1170,17 +1173,17 @@
         <f>B19+2</f>
         <v/>
       </c>
-      <c r="C20" s="33" t="n"/>
-      <c r="D20" s="33" t="n"/>
-      <c r="E20" s="33" t="n"/>
+      <c r="C20" s="47" t="n"/>
+      <c r="D20" s="47" t="n"/>
+      <c r="E20" s="47" t="n"/>
       <c r="F20" s="32">
         <f>F19+2</f>
         <v/>
       </c>
-      <c r="G20" s="33" t="n"/>
-      <c r="H20" s="33" t="n"/>
-      <c r="I20" s="33" t="n"/>
-      <c r="J20" s="33">
+      <c r="G20" s="47" t="n"/>
+      <c r="H20" s="47" t="n"/>
+      <c r="I20" s="47" t="n"/>
+      <c r="J20" s="47">
         <f>IF(OR(NOT(ISNUMBER(E20)),NOT(ISNUMBER(I20))),"NULL",E20-I20)</f>
         <v/>
       </c>
@@ -1192,17 +1195,17 @@
         <f>B20+2</f>
         <v/>
       </c>
-      <c r="C21" s="33" t="n"/>
-      <c r="D21" s="33" t="n"/>
-      <c r="E21" s="33" t="n"/>
+      <c r="C21" s="47" t="n"/>
+      <c r="D21" s="47" t="n"/>
+      <c r="E21" s="47" t="n"/>
       <c r="F21" s="32">
         <f>F20+2</f>
         <v/>
       </c>
-      <c r="G21" s="33" t="n"/>
-      <c r="H21" s="33" t="n"/>
-      <c r="I21" s="33" t="n"/>
-      <c r="J21" s="33">
+      <c r="G21" s="47" t="n"/>
+      <c r="H21" s="47" t="n"/>
+      <c r="I21" s="47" t="n"/>
+      <c r="J21" s="47">
         <f>IF(OR(NOT(ISNUMBER(E21)),NOT(ISNUMBER(I21))),"NULL",E21-I21)</f>
         <v/>
       </c>
@@ -1214,17 +1217,17 @@
         <f>B21+2</f>
         <v/>
       </c>
-      <c r="C22" s="33" t="n"/>
-      <c r="D22" s="33" t="n"/>
-      <c r="E22" s="33" t="n"/>
+      <c r="C22" s="47" t="n"/>
+      <c r="D22" s="47" t="n"/>
+      <c r="E22" s="47" t="n"/>
       <c r="F22" s="32">
         <f>F21+2</f>
         <v/>
       </c>
-      <c r="G22" s="33" t="n"/>
-      <c r="H22" s="33" t="n"/>
-      <c r="I22" s="33" t="n"/>
-      <c r="J22" s="33">
+      <c r="G22" s="47" t="n"/>
+      <c r="H22" s="47" t="n"/>
+      <c r="I22" s="47" t="n"/>
+      <c r="J22" s="47">
         <f>IF(OR(NOT(ISNUMBER(E22)),NOT(ISNUMBER(I22))),"NULL",E22-I22)</f>
         <v/>
       </c>
@@ -1236,17 +1239,17 @@
         <f>B22+2</f>
         <v/>
       </c>
-      <c r="C23" s="33" t="n"/>
-      <c r="D23" s="33" t="n"/>
-      <c r="E23" s="33" t="n"/>
+      <c r="C23" s="47" t="n"/>
+      <c r="D23" s="47" t="n"/>
+      <c r="E23" s="47" t="n"/>
       <c r="F23" s="32">
         <f>F22+2</f>
         <v/>
       </c>
-      <c r="G23" s="33" t="n"/>
-      <c r="H23" s="33" t="n"/>
-      <c r="I23" s="33" t="n"/>
-      <c r="J23" s="33">
+      <c r="G23" s="47" t="n"/>
+      <c r="H23" s="47" t="n"/>
+      <c r="I23" s="47" t="n"/>
+      <c r="J23" s="47">
         <f>IF(OR(NOT(ISNUMBER(E23)),NOT(ISNUMBER(I23))),"NULL",E23-I23)</f>
         <v/>
       </c>
@@ -1258,17 +1261,17 @@
         <f>B23+2</f>
         <v/>
       </c>
-      <c r="C24" s="33" t="n"/>
-      <c r="D24" s="33" t="n"/>
-      <c r="E24" s="33" t="n"/>
+      <c r="C24" s="47" t="n"/>
+      <c r="D24" s="47" t="n"/>
+      <c r="E24" s="47" t="n"/>
       <c r="F24" s="32">
         <f>F23+2</f>
         <v/>
       </c>
-      <c r="G24" s="33" t="n"/>
-      <c r="H24" s="33" t="n"/>
-      <c r="I24" s="33" t="n"/>
-      <c r="J24" s="33">
+      <c r="G24" s="47" t="n"/>
+      <c r="H24" s="47" t="n"/>
+      <c r="I24" s="47" t="n"/>
+      <c r="J24" s="47">
         <f>IF(OR(NOT(ISNUMBER(E24)),NOT(ISNUMBER(I24))),"NULL",E24-I24)</f>
         <v/>
       </c>
@@ -1280,17 +1283,17 @@
         <f>B24+2</f>
         <v/>
       </c>
-      <c r="C25" s="33" t="n"/>
-      <c r="D25" s="33" t="n"/>
-      <c r="E25" s="33" t="n"/>
+      <c r="C25" s="47" t="n"/>
+      <c r="D25" s="47" t="n"/>
+      <c r="E25" s="47" t="n"/>
       <c r="F25" s="32">
         <f>F24+2</f>
         <v/>
       </c>
-      <c r="G25" s="33" t="n"/>
-      <c r="H25" s="33" t="n"/>
-      <c r="I25" s="33" t="n"/>
-      <c r="J25" s="33">
+      <c r="G25" s="47" t="n"/>
+      <c r="H25" s="47" t="n"/>
+      <c r="I25" s="47" t="n"/>
+      <c r="J25" s="47">
         <f>IF(OR(NOT(ISNUMBER(E25)),NOT(ISNUMBER(I25))),"NULL",E25-I25)</f>
         <v/>
       </c>
@@ -1302,17 +1305,17 @@
         <f>B25+2</f>
         <v/>
       </c>
-      <c r="C26" s="33" t="n"/>
-      <c r="D26" s="33" t="n"/>
-      <c r="E26" s="33" t="n"/>
+      <c r="C26" s="47" t="n"/>
+      <c r="D26" s="47" t="n"/>
+      <c r="E26" s="47" t="n"/>
       <c r="F26" s="32">
         <f>F25+2</f>
         <v/>
       </c>
-      <c r="G26" s="33" t="n"/>
-      <c r="H26" s="33" t="n"/>
-      <c r="I26" s="33" t="n"/>
-      <c r="J26" s="33">
+      <c r="G26" s="47" t="n"/>
+      <c r="H26" s="47" t="n"/>
+      <c r="I26" s="47" t="n"/>
+      <c r="J26" s="47">
         <f>IF(OR(NOT(ISNUMBER(E26)),NOT(ISNUMBER(I26))),"NULL",E26-I26)</f>
         <v/>
       </c>
@@ -1324,17 +1327,17 @@
         <f>B26+2</f>
         <v/>
       </c>
-      <c r="C27" s="33" t="n"/>
-      <c r="D27" s="33" t="n"/>
-      <c r="E27" s="33" t="n"/>
+      <c r="C27" s="47" t="n"/>
+      <c r="D27" s="47" t="n"/>
+      <c r="E27" s="47" t="n"/>
       <c r="F27" s="32">
         <f>F26+2</f>
         <v/>
       </c>
-      <c r="G27" s="33" t="n"/>
-      <c r="H27" s="33" t="n"/>
-      <c r="I27" s="33" t="n"/>
-      <c r="J27" s="33">
+      <c r="G27" s="47" t="n"/>
+      <c r="H27" s="47" t="n"/>
+      <c r="I27" s="47" t="n"/>
+      <c r="J27" s="47">
         <f>IF(OR(NOT(ISNUMBER(E27)),NOT(ISNUMBER(I27))),"NULL",E27-I27)</f>
         <v/>
       </c>
@@ -1346,17 +1349,17 @@
         <f>B27+2</f>
         <v/>
       </c>
-      <c r="C28" s="33" t="n"/>
-      <c r="D28" s="33" t="n"/>
-      <c r="E28" s="33" t="n"/>
+      <c r="C28" s="47" t="n"/>
+      <c r="D28" s="47" t="n"/>
+      <c r="E28" s="47" t="n"/>
       <c r="F28" s="32">
         <f>F27+2</f>
         <v/>
       </c>
-      <c r="G28" s="33" t="n"/>
-      <c r="H28" s="33" t="n"/>
-      <c r="I28" s="33" t="n"/>
-      <c r="J28" s="33">
+      <c r="G28" s="47" t="n"/>
+      <c r="H28" s="47" t="n"/>
+      <c r="I28" s="47" t="n"/>
+      <c r="J28" s="47">
         <f>IF(OR(NOT(ISNUMBER(E28)),NOT(ISNUMBER(I28))),"NULL",E28-I28)</f>
         <v/>
       </c>
@@ -1368,17 +1371,17 @@
         <f>B28+2</f>
         <v/>
       </c>
-      <c r="C29" s="33" t="n"/>
-      <c r="D29" s="33" t="n"/>
-      <c r="E29" s="33" t="n"/>
+      <c r="C29" s="47" t="n"/>
+      <c r="D29" s="47" t="n"/>
+      <c r="E29" s="47" t="n"/>
       <c r="F29" s="32">
         <f>F28+2</f>
         <v/>
       </c>
-      <c r="G29" s="33" t="n"/>
-      <c r="H29" s="33" t="n"/>
-      <c r="I29" s="33" t="n"/>
-      <c r="J29" s="33">
+      <c r="G29" s="47" t="n"/>
+      <c r="H29" s="47" t="n"/>
+      <c r="I29" s="47" t="n"/>
+      <c r="J29" s="47">
         <f>IF(OR(NOT(ISNUMBER(E29)),NOT(ISNUMBER(I29))),"NULL",E29-I29)</f>
         <v/>
       </c>
@@ -1390,17 +1393,17 @@
         <f>B29+2</f>
         <v/>
       </c>
-      <c r="C30" s="33" t="n"/>
-      <c r="D30" s="33" t="n"/>
-      <c r="E30" s="33" t="n"/>
+      <c r="C30" s="47" t="n"/>
+      <c r="D30" s="47" t="n"/>
+      <c r="E30" s="47" t="n"/>
       <c r="F30" s="32">
         <f>F29+2</f>
         <v/>
       </c>
-      <c r="G30" s="33" t="n"/>
-      <c r="H30" s="33" t="n"/>
-      <c r="I30" s="33" t="n"/>
-      <c r="J30" s="33">
+      <c r="G30" s="47" t="n"/>
+      <c r="H30" s="47" t="n"/>
+      <c r="I30" s="47" t="n"/>
+      <c r="J30" s="47">
         <f>IF(OR(NOT(ISNUMBER(E30)),NOT(ISNUMBER(I30))),"NULL",E30-I30)</f>
         <v/>
       </c>
@@ -1412,17 +1415,17 @@
         <f>B30+2</f>
         <v/>
       </c>
-      <c r="C31" s="33" t="n"/>
-      <c r="D31" s="33" t="n"/>
-      <c r="E31" s="33" t="n"/>
+      <c r="C31" s="47" t="n"/>
+      <c r="D31" s="47" t="n"/>
+      <c r="E31" s="47" t="n"/>
       <c r="F31" s="32">
         <f>F30+2</f>
         <v/>
       </c>
-      <c r="G31" s="33" t="n"/>
-      <c r="H31" s="33" t="n"/>
-      <c r="I31" s="33" t="n"/>
-      <c r="J31" s="33">
+      <c r="G31" s="47" t="n"/>
+      <c r="H31" s="47" t="n"/>
+      <c r="I31" s="47" t="n"/>
+      <c r="J31" s="47">
         <f>IF(OR(NOT(ISNUMBER(E31)),NOT(ISNUMBER(I31))),"NULL",E31-I31)</f>
         <v/>
       </c>
@@ -1434,17 +1437,17 @@
         <f>B31+2</f>
         <v/>
       </c>
-      <c r="C32" s="33" t="n"/>
-      <c r="D32" s="33" t="n"/>
-      <c r="E32" s="33" t="n"/>
+      <c r="C32" s="47" t="n"/>
+      <c r="D32" s="47" t="n"/>
+      <c r="E32" s="47" t="n"/>
       <c r="F32" s="32">
         <f>F31+2</f>
         <v/>
       </c>
-      <c r="G32" s="33" t="n"/>
-      <c r="H32" s="33" t="n"/>
-      <c r="I32" s="33" t="n"/>
-      <c r="J32" s="33">
+      <c r="G32" s="47" t="n"/>
+      <c r="H32" s="47" t="n"/>
+      <c r="I32" s="47" t="n"/>
+      <c r="J32" s="47">
         <f>IF(OR(NOT(ISNUMBER(E32)),NOT(ISNUMBER(I32))),"NULL",E32-I32)</f>
         <v/>
       </c>
@@ -1456,17 +1459,17 @@
         <f>B32+2</f>
         <v/>
       </c>
-      <c r="C33" s="33" t="n"/>
-      <c r="D33" s="33" t="n"/>
-      <c r="E33" s="33" t="n"/>
+      <c r="C33" s="47" t="n"/>
+      <c r="D33" s="47" t="n"/>
+      <c r="E33" s="47" t="n"/>
       <c r="F33" s="32">
         <f>F32+2</f>
         <v/>
       </c>
-      <c r="G33" s="33" t="n"/>
-      <c r="H33" s="33" t="n"/>
-      <c r="I33" s="33" t="n"/>
-      <c r="J33" s="33">
+      <c r="G33" s="47" t="n"/>
+      <c r="H33" s="47" t="n"/>
+      <c r="I33" s="47" t="n"/>
+      <c r="J33" s="47">
         <f>IF(OR(NOT(ISNUMBER(E33)),NOT(ISNUMBER(I33))),"NULL",E33-I33)</f>
         <v/>
       </c>
@@ -1800,17 +1803,17 @@
       <c r="B58" s="32" t="n">
         <v>200</v>
       </c>
-      <c r="C58" s="33" t="n"/>
-      <c r="D58" s="33" t="n"/>
-      <c r="E58" s="33" t="n"/>
+      <c r="C58" s="47" t="n"/>
+      <c r="D58" s="47" t="n"/>
+      <c r="E58" s="47" t="n"/>
       <c r="F58" s="32">
         <f>B58+1</f>
         <v/>
       </c>
-      <c r="G58" s="33" t="n"/>
-      <c r="H58" s="33" t="n"/>
-      <c r="I58" s="33" t="n"/>
-      <c r="J58" s="33">
+      <c r="G58" s="47" t="n"/>
+      <c r="H58" s="47" t="n"/>
+      <c r="I58" s="47" t="n"/>
+      <c r="J58" s="47">
         <f>IF(OR(NOT(ISNUMBER(E58)),NOT(ISNUMBER(I58))),"NULL",E58-I58)</f>
         <v/>
       </c>
@@ -1822,17 +1825,17 @@
         <f>B58+2</f>
         <v/>
       </c>
-      <c r="C59" s="33" t="n"/>
-      <c r="D59" s="33" t="n"/>
-      <c r="E59" s="33" t="n"/>
+      <c r="C59" s="47" t="n"/>
+      <c r="D59" s="47" t="n"/>
+      <c r="E59" s="47" t="n"/>
       <c r="F59" s="32">
         <f>F58+2</f>
         <v/>
       </c>
-      <c r="G59" s="33" t="n"/>
-      <c r="H59" s="33" t="n"/>
-      <c r="I59" s="33" t="n"/>
-      <c r="J59" s="33">
+      <c r="G59" s="47" t="n"/>
+      <c r="H59" s="47" t="n"/>
+      <c r="I59" s="47" t="n"/>
+      <c r="J59" s="47">
         <f>IF(OR(NOT(ISNUMBER(E59)),NOT(ISNUMBER(I59))),"NULL",E59-I59)</f>
         <v/>
       </c>
@@ -1844,17 +1847,17 @@
         <f>B59+2</f>
         <v/>
       </c>
-      <c r="C60" s="33" t="n"/>
-      <c r="D60" s="33" t="n"/>
-      <c r="E60" s="33" t="n"/>
+      <c r="C60" s="47" t="n"/>
+      <c r="D60" s="47" t="n"/>
+      <c r="E60" s="47" t="n"/>
       <c r="F60" s="32">
         <f>F59+2</f>
         <v/>
       </c>
-      <c r="G60" s="33" t="n"/>
-      <c r="H60" s="33" t="n"/>
-      <c r="I60" s="33" t="n"/>
-      <c r="J60" s="33">
+      <c r="G60" s="47" t="n"/>
+      <c r="H60" s="47" t="n"/>
+      <c r="I60" s="47" t="n"/>
+      <c r="J60" s="47">
         <f>IF(OR(NOT(ISNUMBER(E60)),NOT(ISNUMBER(I60))),"NULL",E60-I60)</f>
         <v/>
       </c>
@@ -1866,17 +1869,17 @@
         <f>B60+2</f>
         <v/>
       </c>
-      <c r="C61" s="33" t="n"/>
-      <c r="D61" s="33" t="n"/>
-      <c r="E61" s="33" t="n"/>
+      <c r="C61" s="47" t="n"/>
+      <c r="D61" s="47" t="n"/>
+      <c r="E61" s="47" t="n"/>
       <c r="F61" s="32">
         <f>F60+2</f>
         <v/>
       </c>
-      <c r="G61" s="33" t="n"/>
-      <c r="H61" s="33" t="n"/>
-      <c r="I61" s="33" t="n"/>
-      <c r="J61" s="33">
+      <c r="G61" s="47" t="n"/>
+      <c r="H61" s="47" t="n"/>
+      <c r="I61" s="47" t="n"/>
+      <c r="J61" s="47">
         <f>IF(OR(NOT(ISNUMBER(E61)),NOT(ISNUMBER(I61))),"NULL",E61-I61)</f>
         <v/>
       </c>
@@ -1888,17 +1891,17 @@
         <f>B61+2</f>
         <v/>
       </c>
-      <c r="C62" s="33" t="n"/>
-      <c r="D62" s="33" t="n"/>
-      <c r="E62" s="33" t="n"/>
+      <c r="C62" s="47" t="n"/>
+      <c r="D62" s="47" t="n"/>
+      <c r="E62" s="47" t="n"/>
       <c r="F62" s="32">
         <f>F61+2</f>
         <v/>
       </c>
-      <c r="G62" s="33" t="n"/>
-      <c r="H62" s="33" t="n"/>
-      <c r="I62" s="33" t="n"/>
-      <c r="J62" s="33">
+      <c r="G62" s="47" t="n"/>
+      <c r="H62" s="47" t="n"/>
+      <c r="I62" s="47" t="n"/>
+      <c r="J62" s="47">
         <f>IF(OR(NOT(ISNUMBER(E62)),NOT(ISNUMBER(I62))),"NULL",E62-I62)</f>
         <v/>
       </c>
@@ -1910,17 +1913,17 @@
         <f>B62+2</f>
         <v/>
       </c>
-      <c r="C63" s="33" t="n"/>
-      <c r="D63" s="33" t="n"/>
-      <c r="E63" s="33" t="n"/>
+      <c r="C63" s="47" t="n"/>
+      <c r="D63" s="47" t="n"/>
+      <c r="E63" s="47" t="n"/>
       <c r="F63" s="32">
         <f>F62+2</f>
         <v/>
       </c>
-      <c r="G63" s="33" t="n"/>
-      <c r="H63" s="33" t="n"/>
-      <c r="I63" s="33" t="n"/>
-      <c r="J63" s="33">
+      <c r="G63" s="47" t="n"/>
+      <c r="H63" s="47" t="n"/>
+      <c r="I63" s="47" t="n"/>
+      <c r="J63" s="47">
         <f>IF(OR(NOT(ISNUMBER(E63)),NOT(ISNUMBER(I63))),"NULL",E63-I63)</f>
         <v/>
       </c>
@@ -1932,17 +1935,17 @@
         <f>B63+2</f>
         <v/>
       </c>
-      <c r="C64" s="33" t="n"/>
-      <c r="D64" s="33" t="n"/>
-      <c r="E64" s="33" t="n"/>
+      <c r="C64" s="47" t="n"/>
+      <c r="D64" s="47" t="n"/>
+      <c r="E64" s="47" t="n"/>
       <c r="F64" s="32">
         <f>F63+2</f>
         <v/>
       </c>
-      <c r="G64" s="33" t="n"/>
-      <c r="H64" s="33" t="n"/>
-      <c r="I64" s="33" t="n"/>
-      <c r="J64" s="33">
+      <c r="G64" s="47" t="n"/>
+      <c r="H64" s="47" t="n"/>
+      <c r="I64" s="47" t="n"/>
+      <c r="J64" s="47">
         <f>IF(OR(NOT(ISNUMBER(E64)),NOT(ISNUMBER(I64))),"NULL",E64-I64)</f>
         <v/>
       </c>
@@ -1954,17 +1957,17 @@
         <f>B64+2</f>
         <v/>
       </c>
-      <c r="C65" s="33" t="n"/>
-      <c r="D65" s="33" t="n"/>
-      <c r="E65" s="33" t="n"/>
+      <c r="C65" s="47" t="n"/>
+      <c r="D65" s="47" t="n"/>
+      <c r="E65" s="47" t="n"/>
       <c r="F65" s="32">
         <f>F64+2</f>
         <v/>
       </c>
-      <c r="G65" s="33" t="n"/>
-      <c r="H65" s="33" t="n"/>
-      <c r="I65" s="33" t="n"/>
-      <c r="J65" s="33">
+      <c r="G65" s="47" t="n"/>
+      <c r="H65" s="47" t="n"/>
+      <c r="I65" s="47" t="n"/>
+      <c r="J65" s="47">
         <f>IF(OR(NOT(ISNUMBER(E65)),NOT(ISNUMBER(I65))),"NULL",E65-I65)</f>
         <v/>
       </c>
@@ -1976,17 +1979,17 @@
         <f>B65+2</f>
         <v/>
       </c>
-      <c r="C66" s="33" t="n"/>
-      <c r="D66" s="33" t="n"/>
-      <c r="E66" s="33" t="n"/>
+      <c r="C66" s="47" t="n"/>
+      <c r="D66" s="47" t="n"/>
+      <c r="E66" s="47" t="n"/>
       <c r="F66" s="32">
         <f>F65+2</f>
         <v/>
       </c>
-      <c r="G66" s="33" t="n"/>
-      <c r="H66" s="33" t="n"/>
-      <c r="I66" s="33" t="n"/>
-      <c r="J66" s="33">
+      <c r="G66" s="47" t="n"/>
+      <c r="H66" s="47" t="n"/>
+      <c r="I66" s="47" t="n"/>
+      <c r="J66" s="47">
         <f>IF(OR(NOT(ISNUMBER(E66)),NOT(ISNUMBER(I66))),"NULL",E66-I66)</f>
         <v/>
       </c>
@@ -1998,17 +2001,17 @@
         <f>B66+2</f>
         <v/>
       </c>
-      <c r="C67" s="33" t="n"/>
-      <c r="D67" s="33" t="n"/>
-      <c r="E67" s="33" t="n"/>
+      <c r="C67" s="47" t="n"/>
+      <c r="D67" s="47" t="n"/>
+      <c r="E67" s="47" t="n"/>
       <c r="F67" s="32">
         <f>F66+2</f>
         <v/>
       </c>
-      <c r="G67" s="33" t="n"/>
-      <c r="H67" s="33" t="n"/>
-      <c r="I67" s="33" t="n"/>
-      <c r="J67" s="33">
+      <c r="G67" s="47" t="n"/>
+      <c r="H67" s="47" t="n"/>
+      <c r="I67" s="47" t="n"/>
+      <c r="J67" s="47">
         <f>IF(OR(NOT(ISNUMBER(E67)),NOT(ISNUMBER(I67))),"NULL",E67-I67)</f>
         <v/>
       </c>
@@ -2020,17 +2023,17 @@
         <f>B67+2</f>
         <v/>
       </c>
-      <c r="C68" s="33" t="n"/>
-      <c r="D68" s="33" t="n"/>
-      <c r="E68" s="33" t="n"/>
+      <c r="C68" s="47" t="n"/>
+      <c r="D68" s="47" t="n"/>
+      <c r="E68" s="47" t="n"/>
       <c r="F68" s="32">
         <f>F67+2</f>
         <v/>
       </c>
-      <c r="G68" s="33" t="n"/>
-      <c r="H68" s="33" t="n"/>
-      <c r="I68" s="33" t="n"/>
-      <c r="J68" s="33">
+      <c r="G68" s="47" t="n"/>
+      <c r="H68" s="47" t="n"/>
+      <c r="I68" s="47" t="n"/>
+      <c r="J68" s="47">
         <f>IF(OR(NOT(ISNUMBER(E68)),NOT(ISNUMBER(I68))),"NULL",E68-I68)</f>
         <v/>
       </c>
@@ -2042,17 +2045,17 @@
         <f>B68+2</f>
         <v/>
       </c>
-      <c r="C69" s="33" t="n"/>
-      <c r="D69" s="33" t="n"/>
-      <c r="E69" s="33" t="n"/>
+      <c r="C69" s="47" t="n"/>
+      <c r="D69" s="47" t="n"/>
+      <c r="E69" s="47" t="n"/>
       <c r="F69" s="32">
         <f>F68+2</f>
         <v/>
       </c>
-      <c r="G69" s="33" t="n"/>
-      <c r="H69" s="33" t="n"/>
-      <c r="I69" s="33" t="n"/>
-      <c r="J69" s="33">
+      <c r="G69" s="47" t="n"/>
+      <c r="H69" s="47" t="n"/>
+      <c r="I69" s="47" t="n"/>
+      <c r="J69" s="47">
         <f>IF(OR(NOT(ISNUMBER(E69)),NOT(ISNUMBER(I69))),"NULL",E69-I69)</f>
         <v/>
       </c>
@@ -2064,17 +2067,17 @@
         <f>B69+2</f>
         <v/>
       </c>
-      <c r="C70" s="33" t="n"/>
-      <c r="D70" s="33" t="n"/>
-      <c r="E70" s="33" t="n"/>
+      <c r="C70" s="47" t="n"/>
+      <c r="D70" s="47" t="n"/>
+      <c r="E70" s="47" t="n"/>
       <c r="F70" s="32">
         <f>F69+2</f>
         <v/>
       </c>
-      <c r="G70" s="33" t="n"/>
-      <c r="H70" s="33" t="n"/>
-      <c r="I70" s="33" t="n"/>
-      <c r="J70" s="33">
+      <c r="G70" s="47" t="n"/>
+      <c r="H70" s="47" t="n"/>
+      <c r="I70" s="47" t="n"/>
+      <c r="J70" s="47">
         <f>IF(OR(NOT(ISNUMBER(E70)),NOT(ISNUMBER(I70))),"NULL",E70-I70)</f>
         <v/>
       </c>
@@ -2086,17 +2089,17 @@
         <f>B70+2</f>
         <v/>
       </c>
-      <c r="C71" s="33" t="n"/>
-      <c r="D71" s="33" t="n"/>
-      <c r="E71" s="33" t="n"/>
+      <c r="C71" s="47" t="n"/>
+      <c r="D71" s="47" t="n"/>
+      <c r="E71" s="47" t="n"/>
       <c r="F71" s="32">
         <f>F70+2</f>
         <v/>
       </c>
-      <c r="G71" s="33" t="n"/>
-      <c r="H71" s="33" t="n"/>
-      <c r="I71" s="33" t="n"/>
-      <c r="J71" s="33">
+      <c r="G71" s="47" t="n"/>
+      <c r="H71" s="47" t="n"/>
+      <c r="I71" s="47" t="n"/>
+      <c r="J71" s="47">
         <f>IF(OR(NOT(ISNUMBER(E71)),NOT(ISNUMBER(I71))),"NULL",E71-I71)</f>
         <v/>
       </c>
@@ -2108,17 +2111,17 @@
         <f>B71+2</f>
         <v/>
       </c>
-      <c r="C72" s="33" t="n"/>
-      <c r="D72" s="33" t="n"/>
-      <c r="E72" s="33" t="n"/>
+      <c r="C72" s="47" t="n"/>
+      <c r="D72" s="47" t="n"/>
+      <c r="E72" s="47" t="n"/>
       <c r="F72" s="32">
         <f>F71+2</f>
         <v/>
       </c>
-      <c r="G72" s="33" t="n"/>
-      <c r="H72" s="33" t="n"/>
-      <c r="I72" s="33" t="n"/>
-      <c r="J72" s="33">
+      <c r="G72" s="47" t="n"/>
+      <c r="H72" s="47" t="n"/>
+      <c r="I72" s="47" t="n"/>
+      <c r="J72" s="47">
         <f>IF(OR(NOT(ISNUMBER(E72)),NOT(ISNUMBER(I72))),"NULL",E72-I72)</f>
         <v/>
       </c>
@@ -2130,17 +2133,17 @@
         <f>B72+2</f>
         <v/>
       </c>
-      <c r="C73" s="33" t="n"/>
-      <c r="D73" s="33" t="n"/>
-      <c r="E73" s="33" t="n"/>
+      <c r="C73" s="47" t="n"/>
+      <c r="D73" s="47" t="n"/>
+      <c r="E73" s="47" t="n"/>
       <c r="F73" s="32">
         <f>F72+2</f>
         <v/>
       </c>
-      <c r="G73" s="33" t="n"/>
-      <c r="H73" s="33" t="n"/>
-      <c r="I73" s="33" t="n"/>
-      <c r="J73" s="33">
+      <c r="G73" s="47" t="n"/>
+      <c r="H73" s="47" t="n"/>
+      <c r="I73" s="47" t="n"/>
+      <c r="J73" s="47">
         <f>IF(OR(NOT(ISNUMBER(E73)),NOT(ISNUMBER(I73))),"NULL",E73-I73)</f>
         <v/>
       </c>
@@ -2152,17 +2155,17 @@
         <f>B73+2</f>
         <v/>
       </c>
-      <c r="C74" s="33" t="n"/>
-      <c r="D74" s="33" t="n"/>
-      <c r="E74" s="33" t="n"/>
+      <c r="C74" s="47" t="n"/>
+      <c r="D74" s="47" t="n"/>
+      <c r="E74" s="47" t="n"/>
       <c r="F74" s="32">
         <f>F73+2</f>
         <v/>
       </c>
-      <c r="G74" s="33" t="n"/>
-      <c r="H74" s="33" t="n"/>
-      <c r="I74" s="33" t="n"/>
-      <c r="J74" s="33">
+      <c r="G74" s="47" t="n"/>
+      <c r="H74" s="47" t="n"/>
+      <c r="I74" s="47" t="n"/>
+      <c r="J74" s="47">
         <f>IF(OR(NOT(ISNUMBER(E74)),NOT(ISNUMBER(I74))),"NULL",E74-I74)</f>
         <v/>
       </c>
@@ -2174,17 +2177,17 @@
         <f>B74+2</f>
         <v/>
       </c>
-      <c r="C75" s="33" t="n"/>
-      <c r="D75" s="33" t="n"/>
-      <c r="E75" s="33" t="n"/>
+      <c r="C75" s="47" t="n"/>
+      <c r="D75" s="47" t="n"/>
+      <c r="E75" s="47" t="n"/>
       <c r="F75" s="32">
         <f>F74+2</f>
         <v/>
       </c>
-      <c r="G75" s="33" t="n"/>
-      <c r="H75" s="33" t="n"/>
-      <c r="I75" s="33" t="n"/>
-      <c r="J75" s="33">
+      <c r="G75" s="47" t="n"/>
+      <c r="H75" s="47" t="n"/>
+      <c r="I75" s="47" t="n"/>
+      <c r="J75" s="47">
         <f>IF(OR(NOT(ISNUMBER(E75)),NOT(ISNUMBER(I75))),"NULL",E75-I75)</f>
         <v/>
       </c>
@@ -2196,17 +2199,17 @@
         <f>B75+2</f>
         <v/>
       </c>
-      <c r="C76" s="33" t="n"/>
-      <c r="D76" s="33" t="n"/>
-      <c r="E76" s="33" t="n"/>
+      <c r="C76" s="47" t="n"/>
+      <c r="D76" s="47" t="n"/>
+      <c r="E76" s="47" t="n"/>
       <c r="F76" s="32">
         <f>F75+2</f>
         <v/>
       </c>
-      <c r="G76" s="33" t="n"/>
-      <c r="H76" s="33" t="n"/>
-      <c r="I76" s="33" t="n"/>
-      <c r="J76" s="33">
+      <c r="G76" s="47" t="n"/>
+      <c r="H76" s="47" t="n"/>
+      <c r="I76" s="47" t="n"/>
+      <c r="J76" s="47">
         <f>IF(OR(NOT(ISNUMBER(E76)),NOT(ISNUMBER(I76))),"NULL",E76-I76)</f>
         <v/>
       </c>
@@ -2540,17 +2543,17 @@
       <c r="B101" s="32" t="n">
         <v>300</v>
       </c>
-      <c r="C101" s="33" t="n"/>
-      <c r="D101" s="33" t="n"/>
-      <c r="E101" s="33" t="n"/>
+      <c r="C101" s="47" t="n"/>
+      <c r="D101" s="47" t="n"/>
+      <c r="E101" s="47" t="n"/>
       <c r="F101" s="32">
         <f>B101+1</f>
         <v/>
       </c>
-      <c r="G101" s="33" t="n"/>
-      <c r="H101" s="33" t="n"/>
-      <c r="I101" s="33" t="n"/>
-      <c r="J101" s="33">
+      <c r="G101" s="47" t="n"/>
+      <c r="H101" s="47" t="n"/>
+      <c r="I101" s="47" t="n"/>
+      <c r="J101" s="47">
         <f>IF(OR(NOT(ISNUMBER(E101)),NOT(ISNUMBER(I101))),"NULL",E101-I101)</f>
         <v/>
       </c>
@@ -2562,17 +2565,17 @@
         <f>B101+2</f>
         <v/>
       </c>
-      <c r="C102" s="33" t="n"/>
-      <c r="D102" s="33" t="n"/>
-      <c r="E102" s="33" t="n"/>
+      <c r="C102" s="47" t="n"/>
+      <c r="D102" s="47" t="n"/>
+      <c r="E102" s="47" t="n"/>
       <c r="F102" s="32">
         <f>F101+2</f>
         <v/>
       </c>
-      <c r="G102" s="33" t="n"/>
-      <c r="H102" s="33" t="n"/>
-      <c r="I102" s="33" t="n"/>
-      <c r="J102" s="33">
+      <c r="G102" s="47" t="n"/>
+      <c r="H102" s="47" t="n"/>
+      <c r="I102" s="47" t="n"/>
+      <c r="J102" s="47">
         <f>IF(OR(NOT(ISNUMBER(E102)),NOT(ISNUMBER(I102))),"NULL",E102-I102)</f>
         <v/>
       </c>
@@ -2584,17 +2587,17 @@
         <f>B102+2</f>
         <v/>
       </c>
-      <c r="C103" s="33" t="n"/>
-      <c r="D103" s="33" t="n"/>
-      <c r="E103" s="33" t="n"/>
+      <c r="C103" s="47" t="n"/>
+      <c r="D103" s="47" t="n"/>
+      <c r="E103" s="47" t="n"/>
       <c r="F103" s="32">
         <f>F102+2</f>
         <v/>
       </c>
-      <c r="G103" s="33" t="n"/>
-      <c r="H103" s="33" t="n"/>
-      <c r="I103" s="33" t="n"/>
-      <c r="J103" s="33">
+      <c r="G103" s="47" t="n"/>
+      <c r="H103" s="47" t="n"/>
+      <c r="I103" s="47" t="n"/>
+      <c r="J103" s="47">
         <f>IF(OR(NOT(ISNUMBER(E103)),NOT(ISNUMBER(I103))),"NULL",E103-I103)</f>
         <v/>
       </c>
@@ -2606,17 +2609,17 @@
         <f>B103+2</f>
         <v/>
       </c>
-      <c r="C104" s="33" t="n"/>
-      <c r="D104" s="33" t="n"/>
-      <c r="E104" s="33" t="n"/>
+      <c r="C104" s="47" t="n"/>
+      <c r="D104" s="47" t="n"/>
+      <c r="E104" s="47" t="n"/>
       <c r="F104" s="32">
         <f>F103+2</f>
         <v/>
       </c>
-      <c r="G104" s="33" t="n"/>
-      <c r="H104" s="33" t="n"/>
-      <c r="I104" s="33" t="n"/>
-      <c r="J104" s="33">
+      <c r="G104" s="47" t="n"/>
+      <c r="H104" s="47" t="n"/>
+      <c r="I104" s="47" t="n"/>
+      <c r="J104" s="47">
         <f>IF(OR(NOT(ISNUMBER(E104)),NOT(ISNUMBER(I104))),"NULL",E104-I104)</f>
         <v/>
       </c>
@@ -2628,17 +2631,17 @@
         <f>B104+2</f>
         <v/>
       </c>
-      <c r="C105" s="33" t="n"/>
-      <c r="D105" s="33" t="n"/>
-      <c r="E105" s="33" t="n"/>
+      <c r="C105" s="47" t="n"/>
+      <c r="D105" s="47" t="n"/>
+      <c r="E105" s="47" t="n"/>
       <c r="F105" s="32">
         <f>F104+2</f>
         <v/>
       </c>
-      <c r="G105" s="33" t="n"/>
-      <c r="H105" s="33" t="n"/>
-      <c r="I105" s="33" t="n"/>
-      <c r="J105" s="33">
+      <c r="G105" s="47" t="n"/>
+      <c r="H105" s="47" t="n"/>
+      <c r="I105" s="47" t="n"/>
+      <c r="J105" s="47">
         <f>IF(OR(NOT(ISNUMBER(E105)),NOT(ISNUMBER(I105))),"NULL",E105-I105)</f>
         <v/>
       </c>
@@ -2650,17 +2653,17 @@
         <f>B105+2</f>
         <v/>
       </c>
-      <c r="C106" s="33" t="n"/>
-      <c r="D106" s="33" t="n"/>
-      <c r="E106" s="33" t="n"/>
+      <c r="C106" s="47" t="n"/>
+      <c r="D106" s="47" t="n"/>
+      <c r="E106" s="47" t="n"/>
       <c r="F106" s="32">
         <f>F105+2</f>
         <v/>
       </c>
-      <c r="G106" s="33" t="n"/>
-      <c r="H106" s="33" t="n"/>
-      <c r="I106" s="33" t="n"/>
-      <c r="J106" s="33">
+      <c r="G106" s="47" t="n"/>
+      <c r="H106" s="47" t="n"/>
+      <c r="I106" s="47" t="n"/>
+      <c r="J106" s="47">
         <f>IF(OR(NOT(ISNUMBER(E106)),NOT(ISNUMBER(I106))),"NULL",E106-I106)</f>
         <v/>
       </c>
@@ -2672,17 +2675,17 @@
         <f>B106+2</f>
         <v/>
       </c>
-      <c r="C107" s="33" t="n"/>
-      <c r="D107" s="33" t="n"/>
-      <c r="E107" s="33" t="n"/>
+      <c r="C107" s="47" t="n"/>
+      <c r="D107" s="47" t="n"/>
+      <c r="E107" s="47" t="n"/>
       <c r="F107" s="32">
         <f>F106+2</f>
         <v/>
       </c>
-      <c r="G107" s="33" t="n"/>
-      <c r="H107" s="33" t="n"/>
-      <c r="I107" s="33" t="n"/>
-      <c r="J107" s="33">
+      <c r="G107" s="47" t="n"/>
+      <c r="H107" s="47" t="n"/>
+      <c r="I107" s="47" t="n"/>
+      <c r="J107" s="47">
         <f>IF(OR(NOT(ISNUMBER(E107)),NOT(ISNUMBER(I107))),"NULL",E107-I107)</f>
         <v/>
       </c>
@@ -2694,17 +2697,17 @@
         <f>B107+2</f>
         <v/>
       </c>
-      <c r="C108" s="33" t="n"/>
-      <c r="D108" s="33" t="n"/>
-      <c r="E108" s="33" t="n"/>
+      <c r="C108" s="47" t="n"/>
+      <c r="D108" s="47" t="n"/>
+      <c r="E108" s="47" t="n"/>
       <c r="F108" s="32">
         <f>F107+2</f>
         <v/>
       </c>
-      <c r="G108" s="33" t="n"/>
-      <c r="H108" s="33" t="n"/>
-      <c r="I108" s="33" t="n"/>
-      <c r="J108" s="33">
+      <c r="G108" s="47" t="n"/>
+      <c r="H108" s="47" t="n"/>
+      <c r="I108" s="47" t="n"/>
+      <c r="J108" s="47">
         <f>IF(OR(NOT(ISNUMBER(E108)),NOT(ISNUMBER(I108))),"NULL",E108-I108)</f>
         <v/>
       </c>
@@ -2716,17 +2719,17 @@
         <f>B108+2</f>
         <v/>
       </c>
-      <c r="C109" s="33" t="n"/>
-      <c r="D109" s="33" t="n"/>
-      <c r="E109" s="33" t="n"/>
+      <c r="C109" s="47" t="n"/>
+      <c r="D109" s="47" t="n"/>
+      <c r="E109" s="47" t="n"/>
       <c r="F109" s="32">
         <f>F108+2</f>
         <v/>
       </c>
-      <c r="G109" s="33" t="n"/>
-      <c r="H109" s="33" t="n"/>
-      <c r="I109" s="33" t="n"/>
-      <c r="J109" s="33">
+      <c r="G109" s="47" t="n"/>
+      <c r="H109" s="47" t="n"/>
+      <c r="I109" s="47" t="n"/>
+      <c r="J109" s="47">
         <f>IF(OR(NOT(ISNUMBER(E109)),NOT(ISNUMBER(I109))),"NULL",E109-I109)</f>
         <v/>
       </c>
@@ -2738,17 +2741,17 @@
         <f>B109+2</f>
         <v/>
       </c>
-      <c r="C110" s="33" t="n"/>
-      <c r="D110" s="33" t="n"/>
-      <c r="E110" s="33" t="n"/>
+      <c r="C110" s="47" t="n"/>
+      <c r="D110" s="47" t="n"/>
+      <c r="E110" s="47" t="n"/>
       <c r="F110" s="32">
         <f>F109+2</f>
         <v/>
       </c>
-      <c r="G110" s="33" t="n"/>
-      <c r="H110" s="33" t="n"/>
-      <c r="I110" s="33" t="n"/>
-      <c r="J110" s="33">
+      <c r="G110" s="47" t="n"/>
+      <c r="H110" s="47" t="n"/>
+      <c r="I110" s="47" t="n"/>
+      <c r="J110" s="47">
         <f>IF(OR(NOT(ISNUMBER(E110)),NOT(ISNUMBER(I110))),"NULL",E110-I110)</f>
         <v/>
       </c>
@@ -2760,17 +2763,17 @@
         <f>B110+2</f>
         <v/>
       </c>
-      <c r="C111" s="33" t="n"/>
-      <c r="D111" s="33" t="n"/>
-      <c r="E111" s="33" t="n"/>
+      <c r="C111" s="47" t="n"/>
+      <c r="D111" s="47" t="n"/>
+      <c r="E111" s="47" t="n"/>
       <c r="F111" s="32">
         <f>F110+2</f>
         <v/>
       </c>
-      <c r="G111" s="33" t="n"/>
-      <c r="H111" s="33" t="n"/>
-      <c r="I111" s="33" t="n"/>
-      <c r="J111" s="33">
+      <c r="G111" s="47" t="n"/>
+      <c r="H111" s="47" t="n"/>
+      <c r="I111" s="47" t="n"/>
+      <c r="J111" s="47">
         <f>IF(OR(NOT(ISNUMBER(E111)),NOT(ISNUMBER(I111))),"NULL",E111-I111)</f>
         <v/>
       </c>
@@ -2782,17 +2785,17 @@
         <f>B111+2</f>
         <v/>
       </c>
-      <c r="C112" s="33" t="n"/>
-      <c r="D112" s="33" t="n"/>
-      <c r="E112" s="33" t="n"/>
+      <c r="C112" s="47" t="n"/>
+      <c r="D112" s="47" t="n"/>
+      <c r="E112" s="47" t="n"/>
       <c r="F112" s="32">
         <f>F111+2</f>
         <v/>
       </c>
-      <c r="G112" s="33" t="n"/>
-      <c r="H112" s="33" t="n"/>
-      <c r="I112" s="33" t="n"/>
-      <c r="J112" s="33">
+      <c r="G112" s="47" t="n"/>
+      <c r="H112" s="47" t="n"/>
+      <c r="I112" s="47" t="n"/>
+      <c r="J112" s="47">
         <f>IF(OR(NOT(ISNUMBER(E112)),NOT(ISNUMBER(I112))),"NULL",E112-I112)</f>
         <v/>
       </c>
@@ -2804,17 +2807,17 @@
         <f>B112+2</f>
         <v/>
       </c>
-      <c r="C113" s="33" t="n"/>
-      <c r="D113" s="33" t="n"/>
-      <c r="E113" s="33" t="n"/>
+      <c r="C113" s="47" t="n"/>
+      <c r="D113" s="47" t="n"/>
+      <c r="E113" s="47" t="n"/>
       <c r="F113" s="32">
         <f>F112+2</f>
         <v/>
       </c>
-      <c r="G113" s="33" t="n"/>
-      <c r="H113" s="33" t="n"/>
-      <c r="I113" s="33" t="n"/>
-      <c r="J113" s="33">
+      <c r="G113" s="47" t="n"/>
+      <c r="H113" s="47" t="n"/>
+      <c r="I113" s="47" t="n"/>
+      <c r="J113" s="47">
         <f>IF(OR(NOT(ISNUMBER(E113)),NOT(ISNUMBER(I113))),"NULL",E113-I113)</f>
         <v/>
       </c>
@@ -2826,17 +2829,17 @@
         <f>B113+2</f>
         <v/>
       </c>
-      <c r="C114" s="33" t="n"/>
-      <c r="D114" s="33" t="n"/>
-      <c r="E114" s="33" t="n"/>
+      <c r="C114" s="47" t="n"/>
+      <c r="D114" s="47" t="n"/>
+      <c r="E114" s="47" t="n"/>
       <c r="F114" s="32">
         <f>F113+2</f>
         <v/>
       </c>
-      <c r="G114" s="33" t="n"/>
-      <c r="H114" s="33" t="n"/>
-      <c r="I114" s="33" t="n"/>
-      <c r="J114" s="33">
+      <c r="G114" s="47" t="n"/>
+      <c r="H114" s="47" t="n"/>
+      <c r="I114" s="47" t="n"/>
+      <c r="J114" s="47">
         <f>IF(OR(NOT(ISNUMBER(E114)),NOT(ISNUMBER(I114))),"NULL",E114-I114)</f>
         <v/>
       </c>
@@ -2848,17 +2851,17 @@
         <f>B114+2</f>
         <v/>
       </c>
-      <c r="C115" s="33" t="n"/>
-      <c r="D115" s="33" t="n"/>
-      <c r="E115" s="33" t="n"/>
+      <c r="C115" s="47" t="n"/>
+      <c r="D115" s="47" t="n"/>
+      <c r="E115" s="47" t="n"/>
       <c r="F115" s="32">
         <f>F114+2</f>
         <v/>
       </c>
-      <c r="G115" s="33" t="n"/>
-      <c r="H115" s="33" t="n"/>
-      <c r="I115" s="33" t="n"/>
-      <c r="J115" s="33">
+      <c r="G115" s="47" t="n"/>
+      <c r="H115" s="47" t="n"/>
+      <c r="I115" s="47" t="n"/>
+      <c r="J115" s="47">
         <f>IF(OR(NOT(ISNUMBER(E115)),NOT(ISNUMBER(I115))),"NULL",E115-I115)</f>
         <v/>
       </c>
@@ -2870,17 +2873,17 @@
         <f>B115+2</f>
         <v/>
       </c>
-      <c r="C116" s="33" t="n"/>
-      <c r="D116" s="33" t="n"/>
-      <c r="E116" s="33" t="n"/>
+      <c r="C116" s="47" t="n"/>
+      <c r="D116" s="47" t="n"/>
+      <c r="E116" s="47" t="n"/>
       <c r="F116" s="32">
         <f>F115+2</f>
         <v/>
       </c>
-      <c r="G116" s="33" t="n"/>
-      <c r="H116" s="33" t="n"/>
-      <c r="I116" s="33" t="n"/>
-      <c r="J116" s="33">
+      <c r="G116" s="47" t="n"/>
+      <c r="H116" s="47" t="n"/>
+      <c r="I116" s="47" t="n"/>
+      <c r="J116" s="47">
         <f>IF(OR(NOT(ISNUMBER(E116)),NOT(ISNUMBER(I116))),"NULL",E116-I116)</f>
         <v/>
       </c>
@@ -2892,17 +2895,17 @@
         <f>B116+2</f>
         <v/>
       </c>
-      <c r="C117" s="33" t="n"/>
-      <c r="D117" s="33" t="n"/>
-      <c r="E117" s="33" t="n"/>
+      <c r="C117" s="47" t="n"/>
+      <c r="D117" s="47" t="n"/>
+      <c r="E117" s="47" t="n"/>
       <c r="F117" s="32">
         <f>F116+2</f>
         <v/>
       </c>
-      <c r="G117" s="33" t="n"/>
-      <c r="H117" s="33" t="n"/>
-      <c r="I117" s="33" t="n"/>
-      <c r="J117" s="33">
+      <c r="G117" s="47" t="n"/>
+      <c r="H117" s="47" t="n"/>
+      <c r="I117" s="47" t="n"/>
+      <c r="J117" s="47">
         <f>IF(OR(NOT(ISNUMBER(E117)),NOT(ISNUMBER(I117))),"NULL",E117-I117)</f>
         <v/>
       </c>
@@ -2914,17 +2917,17 @@
         <f>B117+2</f>
         <v/>
       </c>
-      <c r="C118" s="33" t="n"/>
-      <c r="D118" s="33" t="n"/>
-      <c r="E118" s="33" t="n"/>
+      <c r="C118" s="47" t="n"/>
+      <c r="D118" s="47" t="n"/>
+      <c r="E118" s="47" t="n"/>
       <c r="F118" s="32">
         <f>F117+2</f>
         <v/>
       </c>
-      <c r="G118" s="33" t="n"/>
-      <c r="H118" s="33" t="n"/>
-      <c r="I118" s="33" t="n"/>
-      <c r="J118" s="33">
+      <c r="G118" s="47" t="n"/>
+      <c r="H118" s="47" t="n"/>
+      <c r="I118" s="47" t="n"/>
+      <c r="J118" s="47">
         <f>IF(OR(NOT(ISNUMBER(E118)),NOT(ISNUMBER(I118))),"NULL",E118-I118)</f>
         <v/>
       </c>
@@ -2936,17 +2939,17 @@
         <f>B118+2</f>
         <v/>
       </c>
-      <c r="C119" s="33" t="n"/>
-      <c r="D119" s="33" t="n"/>
-      <c r="E119" s="33" t="n"/>
+      <c r="C119" s="47" t="n"/>
+      <c r="D119" s="47" t="n"/>
+      <c r="E119" s="47" t="n"/>
       <c r="F119" s="32">
         <f>F118+2</f>
         <v/>
       </c>
-      <c r="G119" s="33" t="n"/>
-      <c r="H119" s="33" t="n"/>
-      <c r="I119" s="33" t="n"/>
-      <c r="J119" s="33">
+      <c r="G119" s="47" t="n"/>
+      <c r="H119" s="47" t="n"/>
+      <c r="I119" s="47" t="n"/>
+      <c r="J119" s="47">
         <f>IF(OR(NOT(ISNUMBER(E119)),NOT(ISNUMBER(I119))),"NULL",E119-I119)</f>
         <v/>
       </c>
@@ -3280,17 +3283,17 @@
       <c r="B144" s="32" t="n">
         <v>400</v>
       </c>
-      <c r="C144" s="33" t="n"/>
-      <c r="D144" s="33" t="n"/>
-      <c r="E144" s="33" t="n"/>
+      <c r="C144" s="47" t="n"/>
+      <c r="D144" s="47" t="n"/>
+      <c r="E144" s="47" t="n"/>
       <c r="F144" s="32">
         <f>B144+1</f>
         <v/>
       </c>
-      <c r="G144" s="33" t="n"/>
-      <c r="H144" s="33" t="n"/>
-      <c r="I144" s="33" t="n"/>
-      <c r="J144" s="33">
+      <c r="G144" s="47" t="n"/>
+      <c r="H144" s="47" t="n"/>
+      <c r="I144" s="47" t="n"/>
+      <c r="J144" s="47">
         <f>IF(OR(NOT(ISNUMBER(E144)),NOT(ISNUMBER(I144))),"NULL",E144-I144)</f>
         <v/>
       </c>
@@ -3302,17 +3305,17 @@
         <f>B144+2</f>
         <v/>
       </c>
-      <c r="C145" s="33" t="n"/>
-      <c r="D145" s="33" t="n"/>
-      <c r="E145" s="33" t="n"/>
+      <c r="C145" s="47" t="n"/>
+      <c r="D145" s="47" t="n"/>
+      <c r="E145" s="47" t="n"/>
       <c r="F145" s="32">
         <f>F144+2</f>
         <v/>
       </c>
-      <c r="G145" s="33" t="n"/>
-      <c r="H145" s="33" t="n"/>
-      <c r="I145" s="33" t="n"/>
-      <c r="J145" s="33">
+      <c r="G145" s="47" t="n"/>
+      <c r="H145" s="47" t="n"/>
+      <c r="I145" s="47" t="n"/>
+      <c r="J145" s="47">
         <f>IF(OR(NOT(ISNUMBER(E145)),NOT(ISNUMBER(I145))),"NULL",E145-I145)</f>
         <v/>
       </c>
@@ -3324,17 +3327,17 @@
         <f>B145+2</f>
         <v/>
       </c>
-      <c r="C146" s="33" t="n"/>
-      <c r="D146" s="33" t="n"/>
-      <c r="E146" s="33" t="n"/>
+      <c r="C146" s="47" t="n"/>
+      <c r="D146" s="47" t="n"/>
+      <c r="E146" s="47" t="n"/>
       <c r="F146" s="32">
         <f>F145+2</f>
         <v/>
       </c>
-      <c r="G146" s="33" t="n"/>
-      <c r="H146" s="33" t="n"/>
-      <c r="I146" s="33" t="n"/>
-      <c r="J146" s="33">
+      <c r="G146" s="47" t="n"/>
+      <c r="H146" s="47" t="n"/>
+      <c r="I146" s="47" t="n"/>
+      <c r="J146" s="47">
         <f>IF(OR(NOT(ISNUMBER(E146)),NOT(ISNUMBER(I146))),"NULL",E146-I146)</f>
         <v/>
       </c>
@@ -3346,17 +3349,17 @@
         <f>B146+2</f>
         <v/>
       </c>
-      <c r="C147" s="33" t="n"/>
-      <c r="D147" s="33" t="n"/>
-      <c r="E147" s="33" t="n"/>
+      <c r="C147" s="47" t="n"/>
+      <c r="D147" s="47" t="n"/>
+      <c r="E147" s="47" t="n"/>
       <c r="F147" s="32">
         <f>F146+2</f>
         <v/>
       </c>
-      <c r="G147" s="33" t="n"/>
-      <c r="H147" s="33" t="n"/>
-      <c r="I147" s="33" t="n"/>
-      <c r="J147" s="33">
+      <c r="G147" s="47" t="n"/>
+      <c r="H147" s="47" t="n"/>
+      <c r="I147" s="47" t="n"/>
+      <c r="J147" s="47">
         <f>IF(OR(NOT(ISNUMBER(E147)),NOT(ISNUMBER(I147))),"NULL",E147-I147)</f>
         <v/>
       </c>
@@ -3368,17 +3371,17 @@
         <f>B147+2</f>
         <v/>
       </c>
-      <c r="C148" s="33" t="n"/>
-      <c r="D148" s="33" t="n"/>
-      <c r="E148" s="33" t="n"/>
+      <c r="C148" s="47" t="n"/>
+      <c r="D148" s="47" t="n"/>
+      <c r="E148" s="47" t="n"/>
       <c r="F148" s="32">
         <f>F147+2</f>
         <v/>
       </c>
-      <c r="G148" s="33" t="n"/>
-      <c r="H148" s="33" t="n"/>
-      <c r="I148" s="33" t="n"/>
-      <c r="J148" s="33">
+      <c r="G148" s="47" t="n"/>
+      <c r="H148" s="47" t="n"/>
+      <c r="I148" s="47" t="n"/>
+      <c r="J148" s="47">
         <f>IF(OR(NOT(ISNUMBER(E148)),NOT(ISNUMBER(I148))),"NULL",E148-I148)</f>
         <v/>
       </c>
@@ -3390,17 +3393,17 @@
         <f>B148+2</f>
         <v/>
       </c>
-      <c r="C149" s="33" t="n"/>
-      <c r="D149" s="33" t="n"/>
-      <c r="E149" s="33" t="n"/>
+      <c r="C149" s="47" t="n"/>
+      <c r="D149" s="47" t="n"/>
+      <c r="E149" s="47" t="n"/>
       <c r="F149" s="32">
         <f>F148+2</f>
         <v/>
       </c>
-      <c r="G149" s="33" t="n"/>
-      <c r="H149" s="33" t="n"/>
-      <c r="I149" s="33" t="n"/>
-      <c r="J149" s="33">
+      <c r="G149" s="47" t="n"/>
+      <c r="H149" s="47" t="n"/>
+      <c r="I149" s="47" t="n"/>
+      <c r="J149" s="47">
         <f>IF(OR(NOT(ISNUMBER(E149)),NOT(ISNUMBER(I149))),"NULL",E149-I149)</f>
         <v/>
       </c>
@@ -3412,17 +3415,17 @@
         <f>B149+2</f>
         <v/>
       </c>
-      <c r="C150" s="33" t="n"/>
-      <c r="D150" s="33" t="n"/>
-      <c r="E150" s="33" t="n"/>
+      <c r="C150" s="47" t="n"/>
+      <c r="D150" s="47" t="n"/>
+      <c r="E150" s="47" t="n"/>
       <c r="F150" s="32">
         <f>F149+2</f>
         <v/>
       </c>
-      <c r="G150" s="33" t="n"/>
-      <c r="H150" s="33" t="n"/>
-      <c r="I150" s="33" t="n"/>
-      <c r="J150" s="33">
+      <c r="G150" s="47" t="n"/>
+      <c r="H150" s="47" t="n"/>
+      <c r="I150" s="47" t="n"/>
+      <c r="J150" s="47">
         <f>IF(OR(NOT(ISNUMBER(E150)),NOT(ISNUMBER(I150))),"NULL",E150-I150)</f>
         <v/>
       </c>
@@ -3434,17 +3437,17 @@
         <f>B150+2</f>
         <v/>
       </c>
-      <c r="C151" s="33" t="n"/>
-      <c r="D151" s="33" t="n"/>
-      <c r="E151" s="33" t="n"/>
+      <c r="C151" s="47" t="n"/>
+      <c r="D151" s="47" t="n"/>
+      <c r="E151" s="47" t="n"/>
       <c r="F151" s="32">
         <f>F150+2</f>
         <v/>
       </c>
-      <c r="G151" s="33" t="n"/>
-      <c r="H151" s="33" t="n"/>
-      <c r="I151" s="33" t="n"/>
-      <c r="J151" s="33">
+      <c r="G151" s="47" t="n"/>
+      <c r="H151" s="47" t="n"/>
+      <c r="I151" s="47" t="n"/>
+      <c r="J151" s="47">
         <f>IF(OR(NOT(ISNUMBER(E151)),NOT(ISNUMBER(I151))),"NULL",E151-I151)</f>
         <v/>
       </c>
@@ -3456,17 +3459,17 @@
         <f>B151+2</f>
         <v/>
       </c>
-      <c r="C152" s="33" t="n"/>
-      <c r="D152" s="33" t="n"/>
-      <c r="E152" s="33" t="n"/>
+      <c r="C152" s="47" t="n"/>
+      <c r="D152" s="47" t="n"/>
+      <c r="E152" s="47" t="n"/>
       <c r="F152" s="32">
         <f>F151+2</f>
         <v/>
       </c>
-      <c r="G152" s="33" t="n"/>
-      <c r="H152" s="33" t="n"/>
-      <c r="I152" s="33" t="n"/>
-      <c r="J152" s="33">
+      <c r="G152" s="47" t="n"/>
+      <c r="H152" s="47" t="n"/>
+      <c r="I152" s="47" t="n"/>
+      <c r="J152" s="47">
         <f>IF(OR(NOT(ISNUMBER(E152)),NOT(ISNUMBER(I152))),"NULL",E152-I152)</f>
         <v/>
       </c>
@@ -3478,17 +3481,17 @@
         <f>B152+2</f>
         <v/>
       </c>
-      <c r="C153" s="33" t="n"/>
-      <c r="D153" s="33" t="n"/>
-      <c r="E153" s="33" t="n"/>
+      <c r="C153" s="47" t="n"/>
+      <c r="D153" s="47" t="n"/>
+      <c r="E153" s="47" t="n"/>
       <c r="F153" s="32">
         <f>F152+2</f>
         <v/>
       </c>
-      <c r="G153" s="33" t="n"/>
-      <c r="H153" s="33" t="n"/>
-      <c r="I153" s="33" t="n"/>
-      <c r="J153" s="33">
+      <c r="G153" s="47" t="n"/>
+      <c r="H153" s="47" t="n"/>
+      <c r="I153" s="47" t="n"/>
+      <c r="J153" s="47">
         <f>IF(OR(NOT(ISNUMBER(E153)),NOT(ISNUMBER(I153))),"NULL",E153-I153)</f>
         <v/>
       </c>
@@ -3500,17 +3503,17 @@
         <f>B153+2</f>
         <v/>
       </c>
-      <c r="C154" s="33" t="n"/>
-      <c r="D154" s="33" t="n"/>
-      <c r="E154" s="33" t="n"/>
+      <c r="C154" s="47" t="n"/>
+      <c r="D154" s="47" t="n"/>
+      <c r="E154" s="47" t="n"/>
       <c r="F154" s="32">
         <f>F153+2</f>
         <v/>
       </c>
-      <c r="G154" s="33" t="n"/>
-      <c r="H154" s="33" t="n"/>
-      <c r="I154" s="33" t="n"/>
-      <c r="J154" s="33">
+      <c r="G154" s="47" t="n"/>
+      <c r="H154" s="47" t="n"/>
+      <c r="I154" s="47" t="n"/>
+      <c r="J154" s="47">
         <f>IF(OR(NOT(ISNUMBER(E154)),NOT(ISNUMBER(I154))),"NULL",E154-I154)</f>
         <v/>
       </c>
@@ -3522,17 +3525,17 @@
         <f>B154+2</f>
         <v/>
       </c>
-      <c r="C155" s="33" t="n"/>
-      <c r="D155" s="33" t="n"/>
-      <c r="E155" s="33" t="n"/>
+      <c r="C155" s="47" t="n"/>
+      <c r="D155" s="47" t="n"/>
+      <c r="E155" s="47" t="n"/>
       <c r="F155" s="32">
         <f>F154+2</f>
         <v/>
       </c>
-      <c r="G155" s="33" t="n"/>
-      <c r="H155" s="33" t="n"/>
-      <c r="I155" s="33" t="n"/>
-      <c r="J155" s="33">
+      <c r="G155" s="47" t="n"/>
+      <c r="H155" s="47" t="n"/>
+      <c r="I155" s="47" t="n"/>
+      <c r="J155" s="47">
         <f>IF(OR(NOT(ISNUMBER(E155)),NOT(ISNUMBER(I155))),"NULL",E155-I155)</f>
         <v/>
       </c>
@@ -3544,17 +3547,17 @@
         <f>B155+2</f>
         <v/>
       </c>
-      <c r="C156" s="33" t="n"/>
-      <c r="D156" s="33" t="n"/>
-      <c r="E156" s="33" t="n"/>
+      <c r="C156" s="47" t="n"/>
+      <c r="D156" s="47" t="n"/>
+      <c r="E156" s="47" t="n"/>
       <c r="F156" s="32">
         <f>F155+2</f>
         <v/>
       </c>
-      <c r="G156" s="33" t="n"/>
-      <c r="H156" s="33" t="n"/>
-      <c r="I156" s="33" t="n"/>
-      <c r="J156" s="33">
+      <c r="G156" s="47" t="n"/>
+      <c r="H156" s="47" t="n"/>
+      <c r="I156" s="47" t="n"/>
+      <c r="J156" s="47">
         <f>IF(OR(NOT(ISNUMBER(E156)),NOT(ISNUMBER(I156))),"NULL",E156-I156)</f>
         <v/>
       </c>
@@ -3566,17 +3569,17 @@
         <f>B156+2</f>
         <v/>
       </c>
-      <c r="C157" s="33" t="n"/>
-      <c r="D157" s="33" t="n"/>
-      <c r="E157" s="33" t="n"/>
+      <c r="C157" s="47" t="n"/>
+      <c r="D157" s="47" t="n"/>
+      <c r="E157" s="47" t="n"/>
       <c r="F157" s="32">
         <f>F156+2</f>
         <v/>
       </c>
-      <c r="G157" s="33" t="n"/>
-      <c r="H157" s="33" t="n"/>
-      <c r="I157" s="33" t="n"/>
-      <c r="J157" s="33">
+      <c r="G157" s="47" t="n"/>
+      <c r="H157" s="47" t="n"/>
+      <c r="I157" s="47" t="n"/>
+      <c r="J157" s="47">
         <f>IF(OR(NOT(ISNUMBER(E157)),NOT(ISNUMBER(I157))),"NULL",E157-I157)</f>
         <v/>
       </c>
@@ -3588,17 +3591,17 @@
         <f>B157+2</f>
         <v/>
       </c>
-      <c r="C158" s="33" t="n"/>
-      <c r="D158" s="33" t="n"/>
-      <c r="E158" s="33" t="n"/>
+      <c r="C158" s="47" t="n"/>
+      <c r="D158" s="47" t="n"/>
+      <c r="E158" s="47" t="n"/>
       <c r="F158" s="32">
         <f>F157+2</f>
         <v/>
       </c>
-      <c r="G158" s="33" t="n"/>
-      <c r="H158" s="33" t="n"/>
-      <c r="I158" s="33" t="n"/>
-      <c r="J158" s="33">
+      <c r="G158" s="47" t="n"/>
+      <c r="H158" s="47" t="n"/>
+      <c r="I158" s="47" t="n"/>
+      <c r="J158" s="47">
         <f>IF(OR(NOT(ISNUMBER(E158)),NOT(ISNUMBER(I158))),"NULL",E158-I158)</f>
         <v/>
       </c>
@@ -3610,17 +3613,17 @@
         <f>B158+2</f>
         <v/>
       </c>
-      <c r="C159" s="33" t="n"/>
-      <c r="D159" s="33" t="n"/>
-      <c r="E159" s="33" t="n"/>
+      <c r="C159" s="47" t="n"/>
+      <c r="D159" s="47" t="n"/>
+      <c r="E159" s="47" t="n"/>
       <c r="F159" s="32">
         <f>F158+2</f>
         <v/>
       </c>
-      <c r="G159" s="33" t="n"/>
-      <c r="H159" s="33" t="n"/>
-      <c r="I159" s="33" t="n"/>
-      <c r="J159" s="33">
+      <c r="G159" s="47" t="n"/>
+      <c r="H159" s="47" t="n"/>
+      <c r="I159" s="47" t="n"/>
+      <c r="J159" s="47">
         <f>IF(OR(NOT(ISNUMBER(E159)),NOT(ISNUMBER(I159))),"NULL",E159-I159)</f>
         <v/>
       </c>
@@ -3632,17 +3635,17 @@
         <f>B159+2</f>
         <v/>
       </c>
-      <c r="C160" s="33" t="n"/>
-      <c r="D160" s="33" t="n"/>
-      <c r="E160" s="33" t="n"/>
+      <c r="C160" s="47" t="n"/>
+      <c r="D160" s="47" t="n"/>
+      <c r="E160" s="47" t="n"/>
       <c r="F160" s="32">
         <f>F159+2</f>
         <v/>
       </c>
-      <c r="G160" s="33" t="n"/>
-      <c r="H160" s="33" t="n"/>
-      <c r="I160" s="33" t="n"/>
-      <c r="J160" s="33">
+      <c r="G160" s="47" t="n"/>
+      <c r="H160" s="47" t="n"/>
+      <c r="I160" s="47" t="n"/>
+      <c r="J160" s="47">
         <f>IF(OR(NOT(ISNUMBER(E160)),NOT(ISNUMBER(I160))),"NULL",E160-I160)</f>
         <v/>
       </c>
@@ -3654,17 +3657,17 @@
         <f>B160+2</f>
         <v/>
       </c>
-      <c r="C161" s="33" t="n"/>
-      <c r="D161" s="33" t="n"/>
-      <c r="E161" s="33" t="n"/>
+      <c r="C161" s="47" t="n"/>
+      <c r="D161" s="47" t="n"/>
+      <c r="E161" s="47" t="n"/>
       <c r="F161" s="32">
         <f>F160+2</f>
         <v/>
       </c>
-      <c r="G161" s="33" t="n"/>
-      <c r="H161" s="33" t="n"/>
-      <c r="I161" s="33" t="n"/>
-      <c r="J161" s="33">
+      <c r="G161" s="47" t="n"/>
+      <c r="H161" s="47" t="n"/>
+      <c r="I161" s="47" t="n"/>
+      <c r="J161" s="47">
         <f>IF(OR(NOT(ISNUMBER(E161)),NOT(ISNUMBER(I161))),"NULL",E161-I161)</f>
         <v/>
       </c>
@@ -3676,17 +3679,17 @@
         <f>B161+2</f>
         <v/>
       </c>
-      <c r="C162" s="33" t="n"/>
-      <c r="D162" s="33" t="n"/>
-      <c r="E162" s="33" t="n"/>
+      <c r="C162" s="47" t="n"/>
+      <c r="D162" s="47" t="n"/>
+      <c r="E162" s="47" t="n"/>
       <c r="F162" s="32">
         <f>F161+2</f>
         <v/>
       </c>
-      <c r="G162" s="33" t="n"/>
-      <c r="H162" s="33" t="n"/>
-      <c r="I162" s="33" t="n"/>
-      <c r="J162" s="33">
+      <c r="G162" s="47" t="n"/>
+      <c r="H162" s="47" t="n"/>
+      <c r="I162" s="47" t="n"/>
+      <c r="J162" s="47">
         <f>IF(OR(NOT(ISNUMBER(E162)),NOT(ISNUMBER(I162))),"NULL",E162-I162)</f>
         <v/>
       </c>
@@ -3835,9 +3838,9 @@
           <t>RMP-A</t>
         </is>
       </c>
-      <c r="C4" s="46" t="n"/>
-      <c r="D4" s="46" t="n"/>
-      <c r="E4" s="46" t="n"/>
+      <c r="C4" s="48" t="n"/>
+      <c r="D4" s="48" t="n"/>
+      <c r="E4" s="48" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="46" t="inlineStr">
@@ -3845,9 +3848,9 @@
           <t>RMP-B</t>
         </is>
       </c>
-      <c r="C5" s="46" t="n"/>
-      <c r="D5" s="46" t="n"/>
-      <c r="E5" s="46" t="n"/>
+      <c r="C5" s="48" t="n"/>
+      <c r="D5" s="48" t="n"/>
+      <c r="E5" s="48" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="46" t="inlineStr">
@@ -3855,9 +3858,9 @@
           <t>RMP-C</t>
         </is>
       </c>
-      <c r="C6" s="46" t="n"/>
-      <c r="D6" s="46" t="n"/>
-      <c r="E6" s="46" t="n"/>
+      <c r="C6" s="48" t="n"/>
+      <c r="D6" s="48" t="n"/>
+      <c r="E6" s="48" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/TRACK_MONITORING_REPORT.xlsx
+++ b/TRACK_MONITORING_REPORT.xlsx
@@ -277,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -379,6 +379,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1063,17 +1065,17 @@
       <c r="B15" s="32" t="n">
         <v>100</v>
       </c>
-      <c r="C15" s="47" t="n"/>
-      <c r="D15" s="47" t="n"/>
-      <c r="E15" s="47" t="n"/>
+      <c r="C15" s="49" t="n"/>
+      <c r="D15" s="49" t="n"/>
+      <c r="E15" s="49" t="n"/>
       <c r="F15" s="32">
         <f>B15+1</f>
         <v/>
       </c>
-      <c r="G15" s="47" t="n"/>
-      <c r="H15" s="47" t="n"/>
-      <c r="I15" s="47" t="n"/>
-      <c r="J15" s="47">
+      <c r="G15" s="49" t="n"/>
+      <c r="H15" s="49" t="n"/>
+      <c r="I15" s="49" t="n"/>
+      <c r="J15" s="49">
         <f>IF(OR(NOT(ISNUMBER(E15)),NOT(ISNUMBER(I15))),"NULL",E15-I15)</f>
         <v/>
       </c>
@@ -1085,17 +1087,17 @@
         <f>B15+2</f>
         <v/>
       </c>
-      <c r="C16" s="47" t="n"/>
-      <c r="D16" s="47" t="n"/>
-      <c r="E16" s="47" t="n"/>
+      <c r="C16" s="49" t="n"/>
+      <c r="D16" s="49" t="n"/>
+      <c r="E16" s="49" t="n"/>
       <c r="F16" s="32">
         <f>F15+2</f>
         <v/>
       </c>
-      <c r="G16" s="47" t="n"/>
-      <c r="H16" s="47" t="n"/>
-      <c r="I16" s="47" t="n"/>
-      <c r="J16" s="47">
+      <c r="G16" s="49" t="n"/>
+      <c r="H16" s="49" t="n"/>
+      <c r="I16" s="49" t="n"/>
+      <c r="J16" s="49">
         <f>IF(OR(NOT(ISNUMBER(E16)),NOT(ISNUMBER(I16))),"NULL",E16-I16)</f>
         <v/>
       </c>
@@ -1107,17 +1109,17 @@
         <f>B16+2</f>
         <v/>
       </c>
-      <c r="C17" s="47" t="n"/>
-      <c r="D17" s="47" t="n"/>
-      <c r="E17" s="47" t="n"/>
+      <c r="C17" s="49" t="n"/>
+      <c r="D17" s="49" t="n"/>
+      <c r="E17" s="49" t="n"/>
       <c r="F17" s="32">
         <f>F16+2</f>
         <v/>
       </c>
-      <c r="G17" s="47" t="n"/>
-      <c r="H17" s="47" t="n"/>
-      <c r="I17" s="47" t="n"/>
-      <c r="J17" s="47">
+      <c r="G17" s="49" t="n"/>
+      <c r="H17" s="49" t="n"/>
+      <c r="I17" s="49" t="n"/>
+      <c r="J17" s="49">
         <f>IF(OR(NOT(ISNUMBER(E17)),NOT(ISNUMBER(I17))),"NULL",E17-I17)</f>
         <v/>
       </c>
@@ -1129,17 +1131,17 @@
         <f>B17+2</f>
         <v/>
       </c>
-      <c r="C18" s="47" t="n"/>
-      <c r="D18" s="47" t="n"/>
-      <c r="E18" s="47" t="n"/>
+      <c r="C18" s="49" t="n"/>
+      <c r="D18" s="49" t="n"/>
+      <c r="E18" s="49" t="n"/>
       <c r="F18" s="32">
         <f>F17+2</f>
         <v/>
       </c>
-      <c r="G18" s="47" t="n"/>
-      <c r="H18" s="47" t="n"/>
-      <c r="I18" s="47" t="n"/>
-      <c r="J18" s="47">
+      <c r="G18" s="49" t="n"/>
+      <c r="H18" s="49" t="n"/>
+      <c r="I18" s="49" t="n"/>
+      <c r="J18" s="49">
         <f>IF(OR(NOT(ISNUMBER(E18)),NOT(ISNUMBER(I18))),"NULL",E18-I18)</f>
         <v/>
       </c>
@@ -1151,17 +1153,17 @@
         <f>B18+2</f>
         <v/>
       </c>
-      <c r="C19" s="47" t="n"/>
-      <c r="D19" s="47" t="n"/>
-      <c r="E19" s="47" t="n"/>
+      <c r="C19" s="49" t="n"/>
+      <c r="D19" s="49" t="n"/>
+      <c r="E19" s="49" t="n"/>
       <c r="F19" s="32">
         <f>F18+2</f>
         <v/>
       </c>
-      <c r="G19" s="47" t="n"/>
-      <c r="H19" s="47" t="n"/>
-      <c r="I19" s="47" t="n"/>
-      <c r="J19" s="47">
+      <c r="G19" s="49" t="n"/>
+      <c r="H19" s="49" t="n"/>
+      <c r="I19" s="49" t="n"/>
+      <c r="J19" s="49">
         <f>IF(OR(NOT(ISNUMBER(E19)),NOT(ISNUMBER(I19))),"NULL",E19-I19)</f>
         <v/>
       </c>
@@ -1173,17 +1175,17 @@
         <f>B19+2</f>
         <v/>
       </c>
-      <c r="C20" s="47" t="n"/>
-      <c r="D20" s="47" t="n"/>
-      <c r="E20" s="47" t="n"/>
+      <c r="C20" s="49" t="n"/>
+      <c r="D20" s="49" t="n"/>
+      <c r="E20" s="49" t="n"/>
       <c r="F20" s="32">
         <f>F19+2</f>
         <v/>
       </c>
-      <c r="G20" s="47" t="n"/>
-      <c r="H20" s="47" t="n"/>
-      <c r="I20" s="47" t="n"/>
-      <c r="J20" s="47">
+      <c r="G20" s="49" t="n"/>
+      <c r="H20" s="49" t="n"/>
+      <c r="I20" s="49" t="n"/>
+      <c r="J20" s="49">
         <f>IF(OR(NOT(ISNUMBER(E20)),NOT(ISNUMBER(I20))),"NULL",E20-I20)</f>
         <v/>
       </c>
@@ -1195,17 +1197,17 @@
         <f>B20+2</f>
         <v/>
       </c>
-      <c r="C21" s="47" t="n"/>
-      <c r="D21" s="47" t="n"/>
-      <c r="E21" s="47" t="n"/>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+      <c r="E21" s="49" t="n"/>
       <c r="F21" s="32">
         <f>F20+2</f>
         <v/>
       </c>
-      <c r="G21" s="47" t="n"/>
-      <c r="H21" s="47" t="n"/>
-      <c r="I21" s="47" t="n"/>
-      <c r="J21" s="47">
+      <c r="G21" s="49" t="n"/>
+      <c r="H21" s="49" t="n"/>
+      <c r="I21" s="49" t="n"/>
+      <c r="J21" s="49">
         <f>IF(OR(NOT(ISNUMBER(E21)),NOT(ISNUMBER(I21))),"NULL",E21-I21)</f>
         <v/>
       </c>
@@ -1217,17 +1219,17 @@
         <f>B21+2</f>
         <v/>
       </c>
-      <c r="C22" s="47" t="n"/>
-      <c r="D22" s="47" t="n"/>
-      <c r="E22" s="47" t="n"/>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+      <c r="E22" s="49" t="n"/>
       <c r="F22" s="32">
         <f>F21+2</f>
         <v/>
       </c>
-      <c r="G22" s="47" t="n"/>
-      <c r="H22" s="47" t="n"/>
-      <c r="I22" s="47" t="n"/>
-      <c r="J22" s="47">
+      <c r="G22" s="49" t="n"/>
+      <c r="H22" s="49" t="n"/>
+      <c r="I22" s="49" t="n"/>
+      <c r="J22" s="49">
         <f>IF(OR(NOT(ISNUMBER(E22)),NOT(ISNUMBER(I22))),"NULL",E22-I22)</f>
         <v/>
       </c>
@@ -1239,17 +1241,17 @@
         <f>B22+2</f>
         <v/>
       </c>
-      <c r="C23" s="47" t="n"/>
-      <c r="D23" s="47" t="n"/>
-      <c r="E23" s="47" t="n"/>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+      <c r="E23" s="49" t="n"/>
       <c r="F23" s="32">
         <f>F22+2</f>
         <v/>
       </c>
-      <c r="G23" s="47" t="n"/>
-      <c r="H23" s="47" t="n"/>
-      <c r="I23" s="47" t="n"/>
-      <c r="J23" s="47">
+      <c r="G23" s="49" t="n"/>
+      <c r="H23" s="49" t="n"/>
+      <c r="I23" s="49" t="n"/>
+      <c r="J23" s="49">
         <f>IF(OR(NOT(ISNUMBER(E23)),NOT(ISNUMBER(I23))),"NULL",E23-I23)</f>
         <v/>
       </c>
@@ -1261,17 +1263,17 @@
         <f>B23+2</f>
         <v/>
       </c>
-      <c r="C24" s="47" t="n"/>
-      <c r="D24" s="47" t="n"/>
-      <c r="E24" s="47" t="n"/>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+      <c r="E24" s="49" t="n"/>
       <c r="F24" s="32">
         <f>F23+2</f>
         <v/>
       </c>
-      <c r="G24" s="47" t="n"/>
-      <c r="H24" s="47" t="n"/>
-      <c r="I24" s="47" t="n"/>
-      <c r="J24" s="47">
+      <c r="G24" s="49" t="n"/>
+      <c r="H24" s="49" t="n"/>
+      <c r="I24" s="49" t="n"/>
+      <c r="J24" s="49">
         <f>IF(OR(NOT(ISNUMBER(E24)),NOT(ISNUMBER(I24))),"NULL",E24-I24)</f>
         <v/>
       </c>
@@ -1283,17 +1285,17 @@
         <f>B24+2</f>
         <v/>
       </c>
-      <c r="C25" s="47" t="n"/>
-      <c r="D25" s="47" t="n"/>
-      <c r="E25" s="47" t="n"/>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+      <c r="E25" s="49" t="n"/>
       <c r="F25" s="32">
         <f>F24+2</f>
         <v/>
       </c>
-      <c r="G25" s="47" t="n"/>
-      <c r="H25" s="47" t="n"/>
-      <c r="I25" s="47" t="n"/>
-      <c r="J25" s="47">
+      <c r="G25" s="49" t="n"/>
+      <c r="H25" s="49" t="n"/>
+      <c r="I25" s="49" t="n"/>
+      <c r="J25" s="49">
         <f>IF(OR(NOT(ISNUMBER(E25)),NOT(ISNUMBER(I25))),"NULL",E25-I25)</f>
         <v/>
       </c>
@@ -1305,17 +1307,17 @@
         <f>B25+2</f>
         <v/>
       </c>
-      <c r="C26" s="47" t="n"/>
-      <c r="D26" s="47" t="n"/>
-      <c r="E26" s="47" t="n"/>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+      <c r="E26" s="49" t="n"/>
       <c r="F26" s="32">
         <f>F25+2</f>
         <v/>
       </c>
-      <c r="G26" s="47" t="n"/>
-      <c r="H26" s="47" t="n"/>
-      <c r="I26" s="47" t="n"/>
-      <c r="J26" s="47">
+      <c r="G26" s="49" t="n"/>
+      <c r="H26" s="49" t="n"/>
+      <c r="I26" s="49" t="n"/>
+      <c r="J26" s="49">
         <f>IF(OR(NOT(ISNUMBER(E26)),NOT(ISNUMBER(I26))),"NULL",E26-I26)</f>
         <v/>
       </c>
@@ -1327,17 +1329,17 @@
         <f>B26+2</f>
         <v/>
       </c>
-      <c r="C27" s="47" t="n"/>
-      <c r="D27" s="47" t="n"/>
-      <c r="E27" s="47" t="n"/>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+      <c r="E27" s="49" t="n"/>
       <c r="F27" s="32">
         <f>F26+2</f>
         <v/>
       </c>
-      <c r="G27" s="47" t="n"/>
-      <c r="H27" s="47" t="n"/>
-      <c r="I27" s="47" t="n"/>
-      <c r="J27" s="47">
+      <c r="G27" s="49" t="n"/>
+      <c r="H27" s="49" t="n"/>
+      <c r="I27" s="49" t="n"/>
+      <c r="J27" s="49">
         <f>IF(OR(NOT(ISNUMBER(E27)),NOT(ISNUMBER(I27))),"NULL",E27-I27)</f>
         <v/>
       </c>
@@ -1349,17 +1351,17 @@
         <f>B27+2</f>
         <v/>
       </c>
-      <c r="C28" s="47" t="n"/>
-      <c r="D28" s="47" t="n"/>
-      <c r="E28" s="47" t="n"/>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+      <c r="E28" s="49" t="n"/>
       <c r="F28" s="32">
         <f>F27+2</f>
         <v/>
       </c>
-      <c r="G28" s="47" t="n"/>
-      <c r="H28" s="47" t="n"/>
-      <c r="I28" s="47" t="n"/>
-      <c r="J28" s="47">
+      <c r="G28" s="49" t="n"/>
+      <c r="H28" s="49" t="n"/>
+      <c r="I28" s="49" t="n"/>
+      <c r="J28" s="49">
         <f>IF(OR(NOT(ISNUMBER(E28)),NOT(ISNUMBER(I28))),"NULL",E28-I28)</f>
         <v/>
       </c>
@@ -1371,17 +1373,17 @@
         <f>B28+2</f>
         <v/>
       </c>
-      <c r="C29" s="47" t="n"/>
-      <c r="D29" s="47" t="n"/>
-      <c r="E29" s="47" t="n"/>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+      <c r="E29" s="49" t="n"/>
       <c r="F29" s="32">
         <f>F28+2</f>
         <v/>
       </c>
-      <c r="G29" s="47" t="n"/>
-      <c r="H29" s="47" t="n"/>
-      <c r="I29" s="47" t="n"/>
-      <c r="J29" s="47">
+      <c r="G29" s="49" t="n"/>
+      <c r="H29" s="49" t="n"/>
+      <c r="I29" s="49" t="n"/>
+      <c r="J29" s="49">
         <f>IF(OR(NOT(ISNUMBER(E29)),NOT(ISNUMBER(I29))),"NULL",E29-I29)</f>
         <v/>
       </c>
@@ -1393,17 +1395,17 @@
         <f>B29+2</f>
         <v/>
       </c>
-      <c r="C30" s="47" t="n"/>
-      <c r="D30" s="47" t="n"/>
-      <c r="E30" s="47" t="n"/>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+      <c r="E30" s="49" t="n"/>
       <c r="F30" s="32">
         <f>F29+2</f>
         <v/>
       </c>
-      <c r="G30" s="47" t="n"/>
-      <c r="H30" s="47" t="n"/>
-      <c r="I30" s="47" t="n"/>
-      <c r="J30" s="47">
+      <c r="G30" s="49" t="n"/>
+      <c r="H30" s="49" t="n"/>
+      <c r="I30" s="49" t="n"/>
+      <c r="J30" s="49">
         <f>IF(OR(NOT(ISNUMBER(E30)),NOT(ISNUMBER(I30))),"NULL",E30-I30)</f>
         <v/>
       </c>
@@ -1415,17 +1417,17 @@
         <f>B30+2</f>
         <v/>
       </c>
-      <c r="C31" s="47" t="n"/>
-      <c r="D31" s="47" t="n"/>
-      <c r="E31" s="47" t="n"/>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+      <c r="E31" s="49" t="n"/>
       <c r="F31" s="32">
         <f>F30+2</f>
         <v/>
       </c>
-      <c r="G31" s="47" t="n"/>
-      <c r="H31" s="47" t="n"/>
-      <c r="I31" s="47" t="n"/>
-      <c r="J31" s="47">
+      <c r="G31" s="49" t="n"/>
+      <c r="H31" s="49" t="n"/>
+      <c r="I31" s="49" t="n"/>
+      <c r="J31" s="49">
         <f>IF(OR(NOT(ISNUMBER(E31)),NOT(ISNUMBER(I31))),"NULL",E31-I31)</f>
         <v/>
       </c>
@@ -1437,17 +1439,17 @@
         <f>B31+2</f>
         <v/>
       </c>
-      <c r="C32" s="47" t="n"/>
-      <c r="D32" s="47" t="n"/>
-      <c r="E32" s="47" t="n"/>
+      <c r="C32" s="49" t="n"/>
+      <c r="D32" s="49" t="n"/>
+      <c r="E32" s="49" t="n"/>
       <c r="F32" s="32">
         <f>F31+2</f>
         <v/>
       </c>
-      <c r="G32" s="47" t="n"/>
-      <c r="H32" s="47" t="n"/>
-      <c r="I32" s="47" t="n"/>
-      <c r="J32" s="47">
+      <c r="G32" s="49" t="n"/>
+      <c r="H32" s="49" t="n"/>
+      <c r="I32" s="49" t="n"/>
+      <c r="J32" s="49">
         <f>IF(OR(NOT(ISNUMBER(E32)),NOT(ISNUMBER(I32))),"NULL",E32-I32)</f>
         <v/>
       </c>
@@ -1459,17 +1461,17 @@
         <f>B32+2</f>
         <v/>
       </c>
-      <c r="C33" s="47" t="n"/>
-      <c r="D33" s="47" t="n"/>
-      <c r="E33" s="47" t="n"/>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+      <c r="E33" s="49" t="n"/>
       <c r="F33" s="32">
         <f>F32+2</f>
         <v/>
       </c>
-      <c r="G33" s="47" t="n"/>
-      <c r="H33" s="47" t="n"/>
-      <c r="I33" s="47" t="n"/>
-      <c r="J33" s="47">
+      <c r="G33" s="49" t="n"/>
+      <c r="H33" s="49" t="n"/>
+      <c r="I33" s="49" t="n"/>
+      <c r="J33" s="49">
         <f>IF(OR(NOT(ISNUMBER(E33)),NOT(ISNUMBER(I33))),"NULL",E33-I33)</f>
         <v/>
       </c>
@@ -1803,17 +1805,17 @@
       <c r="B58" s="32" t="n">
         <v>200</v>
       </c>
-      <c r="C58" s="47" t="n"/>
-      <c r="D58" s="47" t="n"/>
-      <c r="E58" s="47" t="n"/>
+      <c r="C58" s="49" t="n"/>
+      <c r="D58" s="49" t="n"/>
+      <c r="E58" s="49" t="n"/>
       <c r="F58" s="32">
         <f>B58+1</f>
         <v/>
       </c>
-      <c r="G58" s="47" t="n"/>
-      <c r="H58" s="47" t="n"/>
-      <c r="I58" s="47" t="n"/>
-      <c r="J58" s="47">
+      <c r="G58" s="49" t="n"/>
+      <c r="H58" s="49" t="n"/>
+      <c r="I58" s="49" t="n"/>
+      <c r="J58" s="49">
         <f>IF(OR(NOT(ISNUMBER(E58)),NOT(ISNUMBER(I58))),"NULL",E58-I58)</f>
         <v/>
       </c>
@@ -1825,17 +1827,17 @@
         <f>B58+2</f>
         <v/>
       </c>
-      <c r="C59" s="47" t="n"/>
-      <c r="D59" s="47" t="n"/>
-      <c r="E59" s="47" t="n"/>
+      <c r="C59" s="49" t="n"/>
+      <c r="D59" s="49" t="n"/>
+      <c r="E59" s="49" t="n"/>
       <c r="F59" s="32">
         <f>F58+2</f>
         <v/>
       </c>
-      <c r="G59" s="47" t="n"/>
-      <c r="H59" s="47" t="n"/>
-      <c r="I59" s="47" t="n"/>
-      <c r="J59" s="47">
+      <c r="G59" s="49" t="n"/>
+      <c r="H59" s="49" t="n"/>
+      <c r="I59" s="49" t="n"/>
+      <c r="J59" s="49">
         <f>IF(OR(NOT(ISNUMBER(E59)),NOT(ISNUMBER(I59))),"NULL",E59-I59)</f>
         <v/>
       </c>
@@ -1847,17 +1849,17 @@
         <f>B59+2</f>
         <v/>
       </c>
-      <c r="C60" s="47" t="n"/>
-      <c r="D60" s="47" t="n"/>
-      <c r="E60" s="47" t="n"/>
+      <c r="C60" s="49" t="n"/>
+      <c r="D60" s="49" t="n"/>
+      <c r="E60" s="49" t="n"/>
       <c r="F60" s="32">
         <f>F59+2</f>
         <v/>
       </c>
-      <c r="G60" s="47" t="n"/>
-      <c r="H60" s="47" t="n"/>
-      <c r="I60" s="47" t="n"/>
-      <c r="J60" s="47">
+      <c r="G60" s="49" t="n"/>
+      <c r="H60" s="49" t="n"/>
+      <c r="I60" s="49" t="n"/>
+      <c r="J60" s="49">
         <f>IF(OR(NOT(ISNUMBER(E60)),NOT(ISNUMBER(I60))),"NULL",E60-I60)</f>
         <v/>
       </c>
@@ -1869,17 +1871,17 @@
         <f>B60+2</f>
         <v/>
       </c>
-      <c r="C61" s="47" t="n"/>
-      <c r="D61" s="47" t="n"/>
-      <c r="E61" s="47" t="n"/>
+      <c r="C61" s="49" t="n"/>
+      <c r="D61" s="49" t="n"/>
+      <c r="E61" s="49" t="n"/>
       <c r="F61" s="32">
         <f>F60+2</f>
         <v/>
       </c>
-      <c r="G61" s="47" t="n"/>
-      <c r="H61" s="47" t="n"/>
-      <c r="I61" s="47" t="n"/>
-      <c r="J61" s="47">
+      <c r="G61" s="49" t="n"/>
+      <c r="H61" s="49" t="n"/>
+      <c r="I61" s="49" t="n"/>
+      <c r="J61" s="49">
         <f>IF(OR(NOT(ISNUMBER(E61)),NOT(ISNUMBER(I61))),"NULL",E61-I61)</f>
         <v/>
       </c>
@@ -1891,17 +1893,17 @@
         <f>B61+2</f>
         <v/>
       </c>
-      <c r="C62" s="47" t="n"/>
-      <c r="D62" s="47" t="n"/>
-      <c r="E62" s="47" t="n"/>
+      <c r="C62" s="49" t="n"/>
+      <c r="D62" s="49" t="n"/>
+      <c r="E62" s="49" t="n"/>
       <c r="F62" s="32">
         <f>F61+2</f>
         <v/>
       </c>
-      <c r="G62" s="47" t="n"/>
-      <c r="H62" s="47" t="n"/>
-      <c r="I62" s="47" t="n"/>
-      <c r="J62" s="47">
+      <c r="G62" s="49" t="n"/>
+      <c r="H62" s="49" t="n"/>
+      <c r="I62" s="49" t="n"/>
+      <c r="J62" s="49">
         <f>IF(OR(NOT(ISNUMBER(E62)),NOT(ISNUMBER(I62))),"NULL",E62-I62)</f>
         <v/>
       </c>
@@ -1913,17 +1915,17 @@
         <f>B62+2</f>
         <v/>
       </c>
-      <c r="C63" s="47" t="n"/>
-      <c r="D63" s="47" t="n"/>
-      <c r="E63" s="47" t="n"/>
+      <c r="C63" s="49" t="n"/>
+      <c r="D63" s="49" t="n"/>
+      <c r="E63" s="49" t="n"/>
       <c r="F63" s="32">
         <f>F62+2</f>
         <v/>
       </c>
-      <c r="G63" s="47" t="n"/>
-      <c r="H63" s="47" t="n"/>
-      <c r="I63" s="47" t="n"/>
-      <c r="J63" s="47">
+      <c r="G63" s="49" t="n"/>
+      <c r="H63" s="49" t="n"/>
+      <c r="I63" s="49" t="n"/>
+      <c r="J63" s="49">
         <f>IF(OR(NOT(ISNUMBER(E63)),NOT(ISNUMBER(I63))),"NULL",E63-I63)</f>
         <v/>
       </c>
@@ -1935,17 +1937,17 @@
         <f>B63+2</f>
         <v/>
       </c>
-      <c r="C64" s="47" t="n"/>
-      <c r="D64" s="47" t="n"/>
-      <c r="E64" s="47" t="n"/>
+      <c r="C64" s="49" t="n"/>
+      <c r="D64" s="49" t="n"/>
+      <c r="E64" s="49" t="n"/>
       <c r="F64" s="32">
         <f>F63+2</f>
         <v/>
       </c>
-      <c r="G64" s="47" t="n"/>
-      <c r="H64" s="47" t="n"/>
-      <c r="I64" s="47" t="n"/>
-      <c r="J64" s="47">
+      <c r="G64" s="49" t="n"/>
+      <c r="H64" s="49" t="n"/>
+      <c r="I64" s="49" t="n"/>
+      <c r="J64" s="49">
         <f>IF(OR(NOT(ISNUMBER(E64)),NOT(ISNUMBER(I64))),"NULL",E64-I64)</f>
         <v/>
       </c>
@@ -1957,17 +1959,17 @@
         <f>B64+2</f>
         <v/>
       </c>
-      <c r="C65" s="47" t="n"/>
-      <c r="D65" s="47" t="n"/>
-      <c r="E65" s="47" t="n"/>
+      <c r="C65" s="49" t="n"/>
+      <c r="D65" s="49" t="n"/>
+      <c r="E65" s="49" t="n"/>
       <c r="F65" s="32">
         <f>F64+2</f>
         <v/>
       </c>
-      <c r="G65" s="47" t="n"/>
-      <c r="H65" s="47" t="n"/>
-      <c r="I65" s="47" t="n"/>
-      <c r="J65" s="47">
+      <c r="G65" s="49" t="n"/>
+      <c r="H65" s="49" t="n"/>
+      <c r="I65" s="49" t="n"/>
+      <c r="J65" s="49">
         <f>IF(OR(NOT(ISNUMBER(E65)),NOT(ISNUMBER(I65))),"NULL",E65-I65)</f>
         <v/>
       </c>
@@ -1979,17 +1981,17 @@
         <f>B65+2</f>
         <v/>
       </c>
-      <c r="C66" s="47" t="n"/>
-      <c r="D66" s="47" t="n"/>
-      <c r="E66" s="47" t="n"/>
+      <c r="C66" s="49" t="n"/>
+      <c r="D66" s="49" t="n"/>
+      <c r="E66" s="49" t="n"/>
       <c r="F66" s="32">
         <f>F65+2</f>
         <v/>
       </c>
-      <c r="G66" s="47" t="n"/>
-      <c r="H66" s="47" t="n"/>
-      <c r="I66" s="47" t="n"/>
-      <c r="J66" s="47">
+      <c r="G66" s="49" t="n"/>
+      <c r="H66" s="49" t="n"/>
+      <c r="I66" s="49" t="n"/>
+      <c r="J66" s="49">
         <f>IF(OR(NOT(ISNUMBER(E66)),NOT(ISNUMBER(I66))),"NULL",E66-I66)</f>
         <v/>
       </c>
@@ -2001,17 +2003,17 @@
         <f>B66+2</f>
         <v/>
       </c>
-      <c r="C67" s="47" t="n"/>
-      <c r="D67" s="47" t="n"/>
-      <c r="E67" s="47" t="n"/>
+      <c r="C67" s="49" t="n"/>
+      <c r="D67" s="49" t="n"/>
+      <c r="E67" s="49" t="n"/>
       <c r="F67" s="32">
         <f>F66+2</f>
         <v/>
       </c>
-      <c r="G67" s="47" t="n"/>
-      <c r="H67" s="47" t="n"/>
-      <c r="I67" s="47" t="n"/>
-      <c r="J67" s="47">
+      <c r="G67" s="49" t="n"/>
+      <c r="H67" s="49" t="n"/>
+      <c r="I67" s="49" t="n"/>
+      <c r="J67" s="49">
         <f>IF(OR(NOT(ISNUMBER(E67)),NOT(ISNUMBER(I67))),"NULL",E67-I67)</f>
         <v/>
       </c>
@@ -2023,17 +2025,17 @@
         <f>B67+2</f>
         <v/>
       </c>
-      <c r="C68" s="47" t="n"/>
-      <c r="D68" s="47" t="n"/>
-      <c r="E68" s="47" t="n"/>
+      <c r="C68" s="49" t="n"/>
+      <c r="D68" s="49" t="n"/>
+      <c r="E68" s="49" t="n"/>
       <c r="F68" s="32">
         <f>F67+2</f>
         <v/>
       </c>
-      <c r="G68" s="47" t="n"/>
-      <c r="H68" s="47" t="n"/>
-      <c r="I68" s="47" t="n"/>
-      <c r="J68" s="47">
+      <c r="G68" s="49" t="n"/>
+      <c r="H68" s="49" t="n"/>
+      <c r="I68" s="49" t="n"/>
+      <c r="J68" s="49">
         <f>IF(OR(NOT(ISNUMBER(E68)),NOT(ISNUMBER(I68))),"NULL",E68-I68)</f>
         <v/>
       </c>
@@ -2045,17 +2047,17 @@
         <f>B68+2</f>
         <v/>
       </c>
-      <c r="C69" s="47" t="n"/>
-      <c r="D69" s="47" t="n"/>
-      <c r="E69" s="47" t="n"/>
+      <c r="C69" s="49" t="n"/>
+      <c r="D69" s="49" t="n"/>
+      <c r="E69" s="49" t="n"/>
       <c r="F69" s="32">
         <f>F68+2</f>
         <v/>
       </c>
-      <c r="G69" s="47" t="n"/>
-      <c r="H69" s="47" t="n"/>
-      <c r="I69" s="47" t="n"/>
-      <c r="J69" s="47">
+      <c r="G69" s="49" t="n"/>
+      <c r="H69" s="49" t="n"/>
+      <c r="I69" s="49" t="n"/>
+      <c r="J69" s="49">
         <f>IF(OR(NOT(ISNUMBER(E69)),NOT(ISNUMBER(I69))),"NULL",E69-I69)</f>
         <v/>
       </c>
@@ -2067,17 +2069,17 @@
         <f>B69+2</f>
         <v/>
       </c>
-      <c r="C70" s="47" t="n"/>
-      <c r="D70" s="47" t="n"/>
-      <c r="E70" s="47" t="n"/>
+      <c r="C70" s="49" t="n"/>
+      <c r="D70" s="49" t="n"/>
+      <c r="E70" s="49" t="n"/>
       <c r="F70" s="32">
         <f>F69+2</f>
         <v/>
       </c>
-      <c r="G70" s="47" t="n"/>
-      <c r="H70" s="47" t="n"/>
-      <c r="I70" s="47" t="n"/>
-      <c r="J70" s="47">
+      <c r="G70" s="49" t="n"/>
+      <c r="H70" s="49" t="n"/>
+      <c r="I70" s="49" t="n"/>
+      <c r="J70" s="49">
         <f>IF(OR(NOT(ISNUMBER(E70)),NOT(ISNUMBER(I70))),"NULL",E70-I70)</f>
         <v/>
       </c>
@@ -2089,17 +2091,17 @@
         <f>B70+2</f>
         <v/>
       </c>
-      <c r="C71" s="47" t="n"/>
-      <c r="D71" s="47" t="n"/>
-      <c r="E71" s="47" t="n"/>
+      <c r="C71" s="49" t="n"/>
+      <c r="D71" s="49" t="n"/>
+      <c r="E71" s="49" t="n"/>
       <c r="F71" s="32">
         <f>F70+2</f>
         <v/>
       </c>
-      <c r="G71" s="47" t="n"/>
-      <c r="H71" s="47" t="n"/>
-      <c r="I71" s="47" t="n"/>
-      <c r="J71" s="47">
+      <c r="G71" s="49" t="n"/>
+      <c r="H71" s="49" t="n"/>
+      <c r="I71" s="49" t="n"/>
+      <c r="J71" s="49">
         <f>IF(OR(NOT(ISNUMBER(E71)),NOT(ISNUMBER(I71))),"NULL",E71-I71)</f>
         <v/>
       </c>
@@ -2111,17 +2113,17 @@
         <f>B71+2</f>
         <v/>
       </c>
-      <c r="C72" s="47" t="n"/>
-      <c r="D72" s="47" t="n"/>
-      <c r="E72" s="47" t="n"/>
+      <c r="C72" s="49" t="n"/>
+      <c r="D72" s="49" t="n"/>
+      <c r="E72" s="49" t="n"/>
       <c r="F72" s="32">
         <f>F71+2</f>
         <v/>
       </c>
-      <c r="G72" s="47" t="n"/>
-      <c r="H72" s="47" t="n"/>
-      <c r="I72" s="47" t="n"/>
-      <c r="J72" s="47">
+      <c r="G72" s="49" t="n"/>
+      <c r="H72" s="49" t="n"/>
+      <c r="I72" s="49" t="n"/>
+      <c r="J72" s="49">
         <f>IF(OR(NOT(ISNUMBER(E72)),NOT(ISNUMBER(I72))),"NULL",E72-I72)</f>
         <v/>
       </c>
@@ -2133,17 +2135,17 @@
         <f>B72+2</f>
         <v/>
       </c>
-      <c r="C73" s="47" t="n"/>
-      <c r="D73" s="47" t="n"/>
-      <c r="E73" s="47" t="n"/>
+      <c r="C73" s="49" t="n"/>
+      <c r="D73" s="49" t="n"/>
+      <c r="E73" s="49" t="n"/>
       <c r="F73" s="32">
         <f>F72+2</f>
         <v/>
       </c>
-      <c r="G73" s="47" t="n"/>
-      <c r="H73" s="47" t="n"/>
-      <c r="I73" s="47" t="n"/>
-      <c r="J73" s="47">
+      <c r="G73" s="49" t="n"/>
+      <c r="H73" s="49" t="n"/>
+      <c r="I73" s="49" t="n"/>
+      <c r="J73" s="49">
         <f>IF(OR(NOT(ISNUMBER(E73)),NOT(ISNUMBER(I73))),"NULL",E73-I73)</f>
         <v/>
       </c>
@@ -2155,17 +2157,17 @@
         <f>B73+2</f>
         <v/>
       </c>
-      <c r="C74" s="47" t="n"/>
-      <c r="D74" s="47" t="n"/>
-      <c r="E74" s="47" t="n"/>
+      <c r="C74" s="49" t="n"/>
+      <c r="D74" s="49" t="n"/>
+      <c r="E74" s="49" t="n"/>
       <c r="F74" s="32">
         <f>F73+2</f>
         <v/>
       </c>
-      <c r="G74" s="47" t="n"/>
-      <c r="H74" s="47" t="n"/>
-      <c r="I74" s="47" t="n"/>
-      <c r="J74" s="47">
+      <c r="G74" s="49" t="n"/>
+      <c r="H74" s="49" t="n"/>
+      <c r="I74" s="49" t="n"/>
+      <c r="J74" s="49">
         <f>IF(OR(NOT(ISNUMBER(E74)),NOT(ISNUMBER(I74))),"NULL",E74-I74)</f>
         <v/>
       </c>
@@ -2177,17 +2179,17 @@
         <f>B74+2</f>
         <v/>
       </c>
-      <c r="C75" s="47" t="n"/>
-      <c r="D75" s="47" t="n"/>
-      <c r="E75" s="47" t="n"/>
+      <c r="C75" s="49" t="n"/>
+      <c r="D75" s="49" t="n"/>
+      <c r="E75" s="49" t="n"/>
       <c r="F75" s="32">
         <f>F74+2</f>
         <v/>
       </c>
-      <c r="G75" s="47" t="n"/>
-      <c r="H75" s="47" t="n"/>
-      <c r="I75" s="47" t="n"/>
-      <c r="J75" s="47">
+      <c r="G75" s="49" t="n"/>
+      <c r="H75" s="49" t="n"/>
+      <c r="I75" s="49" t="n"/>
+      <c r="J75" s="49">
         <f>IF(OR(NOT(ISNUMBER(E75)),NOT(ISNUMBER(I75))),"NULL",E75-I75)</f>
         <v/>
       </c>
@@ -2199,17 +2201,17 @@
         <f>B75+2</f>
         <v/>
       </c>
-      <c r="C76" s="47" t="n"/>
-      <c r="D76" s="47" t="n"/>
-      <c r="E76" s="47" t="n"/>
+      <c r="C76" s="49" t="n"/>
+      <c r="D76" s="49" t="n"/>
+      <c r="E76" s="49" t="n"/>
       <c r="F76" s="32">
         <f>F75+2</f>
         <v/>
       </c>
-      <c r="G76" s="47" t="n"/>
-      <c r="H76" s="47" t="n"/>
-      <c r="I76" s="47" t="n"/>
-      <c r="J76" s="47">
+      <c r="G76" s="49" t="n"/>
+      <c r="H76" s="49" t="n"/>
+      <c r="I76" s="49" t="n"/>
+      <c r="J76" s="49">
         <f>IF(OR(NOT(ISNUMBER(E76)),NOT(ISNUMBER(I76))),"NULL",E76-I76)</f>
         <v/>
       </c>
@@ -2543,17 +2545,17 @@
       <c r="B101" s="32" t="n">
         <v>300</v>
       </c>
-      <c r="C101" s="47" t="n"/>
-      <c r="D101" s="47" t="n"/>
-      <c r="E101" s="47" t="n"/>
+      <c r="C101" s="49" t="n"/>
+      <c r="D101" s="49" t="n"/>
+      <c r="E101" s="49" t="n"/>
       <c r="F101" s="32">
         <f>B101+1</f>
         <v/>
       </c>
-      <c r="G101" s="47" t="n"/>
-      <c r="H101" s="47" t="n"/>
-      <c r="I101" s="47" t="n"/>
-      <c r="J101" s="47">
+      <c r="G101" s="49" t="n"/>
+      <c r="H101" s="49" t="n"/>
+      <c r="I101" s="49" t="n"/>
+      <c r="J101" s="49">
         <f>IF(OR(NOT(ISNUMBER(E101)),NOT(ISNUMBER(I101))),"NULL",E101-I101)</f>
         <v/>
       </c>
@@ -2565,17 +2567,17 @@
         <f>B101+2</f>
         <v/>
       </c>
-      <c r="C102" s="47" t="n"/>
-      <c r="D102" s="47" t="n"/>
-      <c r="E102" s="47" t="n"/>
+      <c r="C102" s="49" t="n"/>
+      <c r="D102" s="49" t="n"/>
+      <c r="E102" s="49" t="n"/>
       <c r="F102" s="32">
         <f>F101+2</f>
         <v/>
       </c>
-      <c r="G102" s="47" t="n"/>
-      <c r="H102" s="47" t="n"/>
-      <c r="I102" s="47" t="n"/>
-      <c r="J102" s="47">
+      <c r="G102" s="49" t="n"/>
+      <c r="H102" s="49" t="n"/>
+      <c r="I102" s="49" t="n"/>
+      <c r="J102" s="49">
         <f>IF(OR(NOT(ISNUMBER(E102)),NOT(ISNUMBER(I102))),"NULL",E102-I102)</f>
         <v/>
       </c>
@@ -2587,17 +2589,17 @@
         <f>B102+2</f>
         <v/>
       </c>
-      <c r="C103" s="47" t="n"/>
-      <c r="D103" s="47" t="n"/>
-      <c r="E103" s="47" t="n"/>
+      <c r="C103" s="49" t="n"/>
+      <c r="D103" s="49" t="n"/>
+      <c r="E103" s="49" t="n"/>
       <c r="F103" s="32">
         <f>F102+2</f>
         <v/>
       </c>
-      <c r="G103" s="47" t="n"/>
-      <c r="H103" s="47" t="n"/>
-      <c r="I103" s="47" t="n"/>
-      <c r="J103" s="47">
+      <c r="G103" s="49" t="n"/>
+      <c r="H103" s="49" t="n"/>
+      <c r="I103" s="49" t="n"/>
+      <c r="J103" s="49">
         <f>IF(OR(NOT(ISNUMBER(E103)),NOT(ISNUMBER(I103))),"NULL",E103-I103)</f>
         <v/>
       </c>
@@ -2609,17 +2611,17 @@
         <f>B103+2</f>
         <v/>
       </c>
-      <c r="C104" s="47" t="n"/>
-      <c r="D104" s="47" t="n"/>
-      <c r="E104" s="47" t="n"/>
+      <c r="C104" s="49" t="n"/>
+      <c r="D104" s="49" t="n"/>
+      <c r="E104" s="49" t="n"/>
       <c r="F104" s="32">
         <f>F103+2</f>
         <v/>
       </c>
-      <c r="G104" s="47" t="n"/>
-      <c r="H104" s="47" t="n"/>
-      <c r="I104" s="47" t="n"/>
-      <c r="J104" s="47">
+      <c r="G104" s="49" t="n"/>
+      <c r="H104" s="49" t="n"/>
+      <c r="I104" s="49" t="n"/>
+      <c r="J104" s="49">
         <f>IF(OR(NOT(ISNUMBER(E104)),NOT(ISNUMBER(I104))),"NULL",E104-I104)</f>
         <v/>
       </c>
@@ -2631,17 +2633,17 @@
         <f>B104+2</f>
         <v/>
       </c>
-      <c r="C105" s="47" t="n"/>
-      <c r="D105" s="47" t="n"/>
-      <c r="E105" s="47" t="n"/>
+      <c r="C105" s="49" t="n"/>
+      <c r="D105" s="49" t="n"/>
+      <c r="E105" s="49" t="n"/>
       <c r="F105" s="32">
         <f>F104+2</f>
         <v/>
       </c>
-      <c r="G105" s="47" t="n"/>
-      <c r="H105" s="47" t="n"/>
-      <c r="I105" s="47" t="n"/>
-      <c r="J105" s="47">
+      <c r="G105" s="49" t="n"/>
+      <c r="H105" s="49" t="n"/>
+      <c r="I105" s="49" t="n"/>
+      <c r="J105" s="49">
         <f>IF(OR(NOT(ISNUMBER(E105)),NOT(ISNUMBER(I105))),"NULL",E105-I105)</f>
         <v/>
       </c>
@@ -2653,17 +2655,17 @@
         <f>B105+2</f>
         <v/>
       </c>
-      <c r="C106" s="47" t="n"/>
-      <c r="D106" s="47" t="n"/>
-      <c r="E106" s="47" t="n"/>
+      <c r="C106" s="49" t="n"/>
+      <c r="D106" s="49" t="n"/>
+      <c r="E106" s="49" t="n"/>
       <c r="F106" s="32">
         <f>F105+2</f>
         <v/>
       </c>
-      <c r="G106" s="47" t="n"/>
-      <c r="H106" s="47" t="n"/>
-      <c r="I106" s="47" t="n"/>
-      <c r="J106" s="47">
+      <c r="G106" s="49" t="n"/>
+      <c r="H106" s="49" t="n"/>
+      <c r="I106" s="49" t="n"/>
+      <c r="J106" s="49">
         <f>IF(OR(NOT(ISNUMBER(E106)),NOT(ISNUMBER(I106))),"NULL",E106-I106)</f>
         <v/>
       </c>
@@ -2675,17 +2677,17 @@
         <f>B106+2</f>
         <v/>
       </c>
-      <c r="C107" s="47" t="n"/>
-      <c r="D107" s="47" t="n"/>
-      <c r="E107" s="47" t="n"/>
+      <c r="C107" s="49" t="n"/>
+      <c r="D107" s="49" t="n"/>
+      <c r="E107" s="49" t="n"/>
       <c r="F107" s="32">
         <f>F106+2</f>
         <v/>
       </c>
-      <c r="G107" s="47" t="n"/>
-      <c r="H107" s="47" t="n"/>
-      <c r="I107" s="47" t="n"/>
-      <c r="J107" s="47">
+      <c r="G107" s="49" t="n"/>
+      <c r="H107" s="49" t="n"/>
+      <c r="I107" s="49" t="n"/>
+      <c r="J107" s="49">
         <f>IF(OR(NOT(ISNUMBER(E107)),NOT(ISNUMBER(I107))),"NULL",E107-I107)</f>
         <v/>
       </c>
@@ -2697,17 +2699,17 @@
         <f>B107+2</f>
         <v/>
       </c>
-      <c r="C108" s="47" t="n"/>
-      <c r="D108" s="47" t="n"/>
-      <c r="E108" s="47" t="n"/>
+      <c r="C108" s="49" t="n"/>
+      <c r="D108" s="49" t="n"/>
+      <c r="E108" s="49" t="n"/>
       <c r="F108" s="32">
         <f>F107+2</f>
         <v/>
       </c>
-      <c r="G108" s="47" t="n"/>
-      <c r="H108" s="47" t="n"/>
-      <c r="I108" s="47" t="n"/>
-      <c r="J108" s="47">
+      <c r="G108" s="49" t="n"/>
+      <c r="H108" s="49" t="n"/>
+      <c r="I108" s="49" t="n"/>
+      <c r="J108" s="49">
         <f>IF(OR(NOT(ISNUMBER(E108)),NOT(ISNUMBER(I108))),"NULL",E108-I108)</f>
         <v/>
       </c>
@@ -2719,17 +2721,17 @@
         <f>B108+2</f>
         <v/>
       </c>
-      <c r="C109" s="47" t="n"/>
-      <c r="D109" s="47" t="n"/>
-      <c r="E109" s="47" t="n"/>
+      <c r="C109" s="49" t="n"/>
+      <c r="D109" s="49" t="n"/>
+      <c r="E109" s="49" t="n"/>
       <c r="F109" s="32">
         <f>F108+2</f>
         <v/>
       </c>
-      <c r="G109" s="47" t="n"/>
-      <c r="H109" s="47" t="n"/>
-      <c r="I109" s="47" t="n"/>
-      <c r="J109" s="47">
+      <c r="G109" s="49" t="n"/>
+      <c r="H109" s="49" t="n"/>
+      <c r="I109" s="49" t="n"/>
+      <c r="J109" s="49">
         <f>IF(OR(NOT(ISNUMBER(E109)),NOT(ISNUMBER(I109))),"NULL",E109-I109)</f>
         <v/>
       </c>
@@ -2741,17 +2743,17 @@
         <f>B109+2</f>
         <v/>
       </c>
-      <c r="C110" s="47" t="n"/>
-      <c r="D110" s="47" t="n"/>
-      <c r="E110" s="47" t="n"/>
+      <c r="C110" s="49" t="n"/>
+      <c r="D110" s="49" t="n"/>
+      <c r="E110" s="49" t="n"/>
       <c r="F110" s="32">
         <f>F109+2</f>
         <v/>
       </c>
-      <c r="G110" s="47" t="n"/>
-      <c r="H110" s="47" t="n"/>
-      <c r="I110" s="47" t="n"/>
-      <c r="J110" s="47">
+      <c r="G110" s="49" t="n"/>
+      <c r="H110" s="49" t="n"/>
+      <c r="I110" s="49" t="n"/>
+      <c r="J110" s="49">
         <f>IF(OR(NOT(ISNUMBER(E110)),NOT(ISNUMBER(I110))),"NULL",E110-I110)</f>
         <v/>
       </c>
@@ -2763,17 +2765,17 @@
         <f>B110+2</f>
         <v/>
       </c>
-      <c r="C111" s="47" t="n"/>
-      <c r="D111" s="47" t="n"/>
-      <c r="E111" s="47" t="n"/>
+      <c r="C111" s="49" t="n"/>
+      <c r="D111" s="49" t="n"/>
+      <c r="E111" s="49" t="n"/>
       <c r="F111" s="32">
         <f>F110+2</f>
         <v/>
       </c>
-      <c r="G111" s="47" t="n"/>
-      <c r="H111" s="47" t="n"/>
-      <c r="I111" s="47" t="n"/>
-      <c r="J111" s="47">
+      <c r="G111" s="49" t="n"/>
+      <c r="H111" s="49" t="n"/>
+      <c r="I111" s="49" t="n"/>
+      <c r="J111" s="49">
         <f>IF(OR(NOT(ISNUMBER(E111)),NOT(ISNUMBER(I111))),"NULL",E111-I111)</f>
         <v/>
       </c>
@@ -2785,17 +2787,17 @@
         <f>B111+2</f>
         <v/>
       </c>
-      <c r="C112" s="47" t="n"/>
-      <c r="D112" s="47" t="n"/>
-      <c r="E112" s="47" t="n"/>
+      <c r="C112" s="49" t="n"/>
+      <c r="D112" s="49" t="n"/>
+      <c r="E112" s="49" t="n"/>
       <c r="F112" s="32">
         <f>F111+2</f>
         <v/>
       </c>
-      <c r="G112" s="47" t="n"/>
-      <c r="H112" s="47" t="n"/>
-      <c r="I112" s="47" t="n"/>
-      <c r="J112" s="47">
+      <c r="G112" s="49" t="n"/>
+      <c r="H112" s="49" t="n"/>
+      <c r="I112" s="49" t="n"/>
+      <c r="J112" s="49">
         <f>IF(OR(NOT(ISNUMBER(E112)),NOT(ISNUMBER(I112))),"NULL",E112-I112)</f>
         <v/>
       </c>
@@ -2807,17 +2809,17 @@
         <f>B112+2</f>
         <v/>
       </c>
-      <c r="C113" s="47" t="n"/>
-      <c r="D113" s="47" t="n"/>
-      <c r="E113" s="47" t="n"/>
+      <c r="C113" s="49" t="n"/>
+      <c r="D113" s="49" t="n"/>
+      <c r="E113" s="49" t="n"/>
       <c r="F113" s="32">
         <f>F112+2</f>
         <v/>
       </c>
-      <c r="G113" s="47" t="n"/>
-      <c r="H113" s="47" t="n"/>
-      <c r="I113" s="47" t="n"/>
-      <c r="J113" s="47">
+      <c r="G113" s="49" t="n"/>
+      <c r="H113" s="49" t="n"/>
+      <c r="I113" s="49" t="n"/>
+      <c r="J113" s="49">
         <f>IF(OR(NOT(ISNUMBER(E113)),NOT(ISNUMBER(I113))),"NULL",E113-I113)</f>
         <v/>
       </c>
@@ -2829,17 +2831,17 @@
         <f>B113+2</f>
         <v/>
       </c>
-      <c r="C114" s="47" t="n"/>
-      <c r="D114" s="47" t="n"/>
-      <c r="E114" s="47" t="n"/>
+      <c r="C114" s="49" t="n"/>
+      <c r="D114" s="49" t="n"/>
+      <c r="E114" s="49" t="n"/>
       <c r="F114" s="32">
         <f>F113+2</f>
         <v/>
       </c>
-      <c r="G114" s="47" t="n"/>
-      <c r="H114" s="47" t="n"/>
-      <c r="I114" s="47" t="n"/>
-      <c r="J114" s="47">
+      <c r="G114" s="49" t="n"/>
+      <c r="H114" s="49" t="n"/>
+      <c r="I114" s="49" t="n"/>
+      <c r="J114" s="49">
         <f>IF(OR(NOT(ISNUMBER(E114)),NOT(ISNUMBER(I114))),"NULL",E114-I114)</f>
         <v/>
       </c>
@@ -2851,17 +2853,17 @@
         <f>B114+2</f>
         <v/>
       </c>
-      <c r="C115" s="47" t="n"/>
-      <c r="D115" s="47" t="n"/>
-      <c r="E115" s="47" t="n"/>
+      <c r="C115" s="49" t="n"/>
+      <c r="D115" s="49" t="n"/>
+      <c r="E115" s="49" t="n"/>
       <c r="F115" s="32">
         <f>F114+2</f>
         <v/>
       </c>
-      <c r="G115" s="47" t="n"/>
-      <c r="H115" s="47" t="n"/>
-      <c r="I115" s="47" t="n"/>
-      <c r="J115" s="47">
+      <c r="G115" s="49" t="n"/>
+      <c r="H115" s="49" t="n"/>
+      <c r="I115" s="49" t="n"/>
+      <c r="J115" s="49">
         <f>IF(OR(NOT(ISNUMBER(E115)),NOT(ISNUMBER(I115))),"NULL",E115-I115)</f>
         <v/>
       </c>
@@ -2873,17 +2875,17 @@
         <f>B115+2</f>
         <v/>
       </c>
-      <c r="C116" s="47" t="n"/>
-      <c r="D116" s="47" t="n"/>
-      <c r="E116" s="47" t="n"/>
+      <c r="C116" s="49" t="n"/>
+      <c r="D116" s="49" t="n"/>
+      <c r="E116" s="49" t="n"/>
       <c r="F116" s="32">
         <f>F115+2</f>
         <v/>
       </c>
-      <c r="G116" s="47" t="n"/>
-      <c r="H116" s="47" t="n"/>
-      <c r="I116" s="47" t="n"/>
-      <c r="J116" s="47">
+      <c r="G116" s="49" t="n"/>
+      <c r="H116" s="49" t="n"/>
+      <c r="I116" s="49" t="n"/>
+      <c r="J116" s="49">
         <f>IF(OR(NOT(ISNUMBER(E116)),NOT(ISNUMBER(I116))),"NULL",E116-I116)</f>
         <v/>
       </c>
@@ -2895,17 +2897,17 @@
         <f>B116+2</f>
         <v/>
       </c>
-      <c r="C117" s="47" t="n"/>
-      <c r="D117" s="47" t="n"/>
-      <c r="E117" s="47" t="n"/>
+      <c r="C117" s="49" t="n"/>
+      <c r="D117" s="49" t="n"/>
+      <c r="E117" s="49" t="n"/>
       <c r="F117" s="32">
         <f>F116+2</f>
         <v/>
       </c>
-      <c r="G117" s="47" t="n"/>
-      <c r="H117" s="47" t="n"/>
-      <c r="I117" s="47" t="n"/>
-      <c r="J117" s="47">
+      <c r="G117" s="49" t="n"/>
+      <c r="H117" s="49" t="n"/>
+      <c r="I117" s="49" t="n"/>
+      <c r="J117" s="49">
         <f>IF(OR(NOT(ISNUMBER(E117)),NOT(ISNUMBER(I117))),"NULL",E117-I117)</f>
         <v/>
       </c>
@@ -2917,17 +2919,17 @@
         <f>B117+2</f>
         <v/>
       </c>
-      <c r="C118" s="47" t="n"/>
-      <c r="D118" s="47" t="n"/>
-      <c r="E118" s="47" t="n"/>
+      <c r="C118" s="49" t="n"/>
+      <c r="D118" s="49" t="n"/>
+      <c r="E118" s="49" t="n"/>
       <c r="F118" s="32">
         <f>F117+2</f>
         <v/>
       </c>
-      <c r="G118" s="47" t="n"/>
-      <c r="H118" s="47" t="n"/>
-      <c r="I118" s="47" t="n"/>
-      <c r="J118" s="47">
+      <c r="G118" s="49" t="n"/>
+      <c r="H118" s="49" t="n"/>
+      <c r="I118" s="49" t="n"/>
+      <c r="J118" s="49">
         <f>IF(OR(NOT(ISNUMBER(E118)),NOT(ISNUMBER(I118))),"NULL",E118-I118)</f>
         <v/>
       </c>
@@ -2939,17 +2941,17 @@
         <f>B118+2</f>
         <v/>
       </c>
-      <c r="C119" s="47" t="n"/>
-      <c r="D119" s="47" t="n"/>
-      <c r="E119" s="47" t="n"/>
+      <c r="C119" s="49" t="n"/>
+      <c r="D119" s="49" t="n"/>
+      <c r="E119" s="49" t="n"/>
       <c r="F119" s="32">
         <f>F118+2</f>
         <v/>
       </c>
-      <c r="G119" s="47" t="n"/>
-      <c r="H119" s="47" t="n"/>
-      <c r="I119" s="47" t="n"/>
-      <c r="J119" s="47">
+      <c r="G119" s="49" t="n"/>
+      <c r="H119" s="49" t="n"/>
+      <c r="I119" s="49" t="n"/>
+      <c r="J119" s="49">
         <f>IF(OR(NOT(ISNUMBER(E119)),NOT(ISNUMBER(I119))),"NULL",E119-I119)</f>
         <v/>
       </c>
@@ -3283,17 +3285,17 @@
       <c r="B144" s="32" t="n">
         <v>400</v>
       </c>
-      <c r="C144" s="47" t="n"/>
-      <c r="D144" s="47" t="n"/>
-      <c r="E144" s="47" t="n"/>
+      <c r="C144" s="49" t="n"/>
+      <c r="D144" s="49" t="n"/>
+      <c r="E144" s="49" t="n"/>
       <c r="F144" s="32">
         <f>B144+1</f>
         <v/>
       </c>
-      <c r="G144" s="47" t="n"/>
-      <c r="H144" s="47" t="n"/>
-      <c r="I144" s="47" t="n"/>
-      <c r="J144" s="47">
+      <c r="G144" s="49" t="n"/>
+      <c r="H144" s="49" t="n"/>
+      <c r="I144" s="49" t="n"/>
+      <c r="J144" s="49">
         <f>IF(OR(NOT(ISNUMBER(E144)),NOT(ISNUMBER(I144))),"NULL",E144-I144)</f>
         <v/>
       </c>
@@ -3305,17 +3307,17 @@
         <f>B144+2</f>
         <v/>
       </c>
-      <c r="C145" s="47" t="n"/>
-      <c r="D145" s="47" t="n"/>
-      <c r="E145" s="47" t="n"/>
+      <c r="C145" s="49" t="n"/>
+      <c r="D145" s="49" t="n"/>
+      <c r="E145" s="49" t="n"/>
       <c r="F145" s="32">
         <f>F144+2</f>
         <v/>
       </c>
-      <c r="G145" s="47" t="n"/>
-      <c r="H145" s="47" t="n"/>
-      <c r="I145" s="47" t="n"/>
-      <c r="J145" s="47">
+      <c r="G145" s="49" t="n"/>
+      <c r="H145" s="49" t="n"/>
+      <c r="I145" s="49" t="n"/>
+      <c r="J145" s="49">
         <f>IF(OR(NOT(ISNUMBER(E145)),NOT(ISNUMBER(I145))),"NULL",E145-I145)</f>
         <v/>
       </c>
@@ -3327,17 +3329,17 @@
         <f>B145+2</f>
         <v/>
       </c>
-      <c r="C146" s="47" t="n"/>
-      <c r="D146" s="47" t="n"/>
-      <c r="E146" s="47" t="n"/>
+      <c r="C146" s="49" t="n"/>
+      <c r="D146" s="49" t="n"/>
+      <c r="E146" s="49" t="n"/>
       <c r="F146" s="32">
         <f>F145+2</f>
         <v/>
       </c>
-      <c r="G146" s="47" t="n"/>
-      <c r="H146" s="47" t="n"/>
-      <c r="I146" s="47" t="n"/>
-      <c r="J146" s="47">
+      <c r="G146" s="49" t="n"/>
+      <c r="H146" s="49" t="n"/>
+      <c r="I146" s="49" t="n"/>
+      <c r="J146" s="49">
         <f>IF(OR(NOT(ISNUMBER(E146)),NOT(ISNUMBER(I146))),"NULL",E146-I146)</f>
         <v/>
       </c>
@@ -3349,17 +3351,17 @@
         <f>B146+2</f>
         <v/>
       </c>
-      <c r="C147" s="47" t="n"/>
-      <c r="D147" s="47" t="n"/>
-      <c r="E147" s="47" t="n"/>
+      <c r="C147" s="49" t="n"/>
+      <c r="D147" s="49" t="n"/>
+      <c r="E147" s="49" t="n"/>
       <c r="F147" s="32">
         <f>F146+2</f>
         <v/>
       </c>
-      <c r="G147" s="47" t="n"/>
-      <c r="H147" s="47" t="n"/>
-      <c r="I147" s="47" t="n"/>
-      <c r="J147" s="47">
+      <c r="G147" s="49" t="n"/>
+      <c r="H147" s="49" t="n"/>
+      <c r="I147" s="49" t="n"/>
+      <c r="J147" s="49">
         <f>IF(OR(NOT(ISNUMBER(E147)),NOT(ISNUMBER(I147))),"NULL",E147-I147)</f>
         <v/>
       </c>
@@ -3371,17 +3373,17 @@
         <f>B147+2</f>
         <v/>
       </c>
-      <c r="C148" s="47" t="n"/>
-      <c r="D148" s="47" t="n"/>
-      <c r="E148" s="47" t="n"/>
+      <c r="C148" s="49" t="n"/>
+      <c r="D148" s="49" t="n"/>
+      <c r="E148" s="49" t="n"/>
       <c r="F148" s="32">
         <f>F147+2</f>
         <v/>
       </c>
-      <c r="G148" s="47" t="n"/>
-      <c r="H148" s="47" t="n"/>
-      <c r="I148" s="47" t="n"/>
-      <c r="J148" s="47">
+      <c r="G148" s="49" t="n"/>
+      <c r="H148" s="49" t="n"/>
+      <c r="I148" s="49" t="n"/>
+      <c r="J148" s="49">
         <f>IF(OR(NOT(ISNUMBER(E148)),NOT(ISNUMBER(I148))),"NULL",E148-I148)</f>
         <v/>
       </c>
@@ -3393,17 +3395,17 @@
         <f>B148+2</f>
         <v/>
       </c>
-      <c r="C149" s="47" t="n"/>
-      <c r="D149" s="47" t="n"/>
-      <c r="E149" s="47" t="n"/>
+      <c r="C149" s="49" t="n"/>
+      <c r="D149" s="49" t="n"/>
+      <c r="E149" s="49" t="n"/>
       <c r="F149" s="32">
         <f>F148+2</f>
         <v/>
       </c>
-      <c r="G149" s="47" t="n"/>
-      <c r="H149" s="47" t="n"/>
-      <c r="I149" s="47" t="n"/>
-      <c r="J149" s="47">
+      <c r="G149" s="49" t="n"/>
+      <c r="H149" s="49" t="n"/>
+      <c r="I149" s="49" t="n"/>
+      <c r="J149" s="49">
         <f>IF(OR(NOT(ISNUMBER(E149)),NOT(ISNUMBER(I149))),"NULL",E149-I149)</f>
         <v/>
       </c>
@@ -3415,17 +3417,17 @@
         <f>B149+2</f>
         <v/>
       </c>
-      <c r="C150" s="47" t="n"/>
-      <c r="D150" s="47" t="n"/>
-      <c r="E150" s="47" t="n"/>
+      <c r="C150" s="49" t="n"/>
+      <c r="D150" s="49" t="n"/>
+      <c r="E150" s="49" t="n"/>
       <c r="F150" s="32">
         <f>F149+2</f>
         <v/>
       </c>
-      <c r="G150" s="47" t="n"/>
-      <c r="H150" s="47" t="n"/>
-      <c r="I150" s="47" t="n"/>
-      <c r="J150" s="47">
+      <c r="G150" s="49" t="n"/>
+      <c r="H150" s="49" t="n"/>
+      <c r="I150" s="49" t="n"/>
+      <c r="J150" s="49">
         <f>IF(OR(NOT(ISNUMBER(E150)),NOT(ISNUMBER(I150))),"NULL",E150-I150)</f>
         <v/>
       </c>
@@ -3437,17 +3439,17 @@
         <f>B150+2</f>
         <v/>
       </c>
-      <c r="C151" s="47" t="n"/>
-      <c r="D151" s="47" t="n"/>
-      <c r="E151" s="47" t="n"/>
+      <c r="C151" s="49" t="n"/>
+      <c r="D151" s="49" t="n"/>
+      <c r="E151" s="49" t="n"/>
       <c r="F151" s="32">
         <f>F150+2</f>
         <v/>
       </c>
-      <c r="G151" s="47" t="n"/>
-      <c r="H151" s="47" t="n"/>
-      <c r="I151" s="47" t="n"/>
-      <c r="J151" s="47">
+      <c r="G151" s="49" t="n"/>
+      <c r="H151" s="49" t="n"/>
+      <c r="I151" s="49" t="n"/>
+      <c r="J151" s="49">
         <f>IF(OR(NOT(ISNUMBER(E151)),NOT(ISNUMBER(I151))),"NULL",E151-I151)</f>
         <v/>
       </c>
@@ -3459,17 +3461,17 @@
         <f>B151+2</f>
         <v/>
       </c>
-      <c r="C152" s="47" t="n"/>
-      <c r="D152" s="47" t="n"/>
-      <c r="E152" s="47" t="n"/>
+      <c r="C152" s="49" t="n"/>
+      <c r="D152" s="49" t="n"/>
+      <c r="E152" s="49" t="n"/>
       <c r="F152" s="32">
         <f>F151+2</f>
         <v/>
       </c>
-      <c r="G152" s="47" t="n"/>
-      <c r="H152" s="47" t="n"/>
-      <c r="I152" s="47" t="n"/>
-      <c r="J152" s="47">
+      <c r="G152" s="49" t="n"/>
+      <c r="H152" s="49" t="n"/>
+      <c r="I152" s="49" t="n"/>
+      <c r="J152" s="49">
         <f>IF(OR(NOT(ISNUMBER(E152)),NOT(ISNUMBER(I152))),"NULL",E152-I152)</f>
         <v/>
       </c>
@@ -3481,17 +3483,17 @@
         <f>B152+2</f>
         <v/>
       </c>
-      <c r="C153" s="47" t="n"/>
-      <c r="D153" s="47" t="n"/>
-      <c r="E153" s="47" t="n"/>
+      <c r="C153" s="49" t="n"/>
+      <c r="D153" s="49" t="n"/>
+      <c r="E153" s="49" t="n"/>
       <c r="F153" s="32">
         <f>F152+2</f>
         <v/>
       </c>
-      <c r="G153" s="47" t="n"/>
-      <c r="H153" s="47" t="n"/>
-      <c r="I153" s="47" t="n"/>
-      <c r="J153" s="47">
+      <c r="G153" s="49" t="n"/>
+      <c r="H153" s="49" t="n"/>
+      <c r="I153" s="49" t="n"/>
+      <c r="J153" s="49">
         <f>IF(OR(NOT(ISNUMBER(E153)),NOT(ISNUMBER(I153))),"NULL",E153-I153)</f>
         <v/>
       </c>
@@ -3503,17 +3505,17 @@
         <f>B153+2</f>
         <v/>
       </c>
-      <c r="C154" s="47" t="n"/>
-      <c r="D154" s="47" t="n"/>
-      <c r="E154" s="47" t="n"/>
+      <c r="C154" s="49" t="n"/>
+      <c r="D154" s="49" t="n"/>
+      <c r="E154" s="49" t="n"/>
       <c r="F154" s="32">
         <f>F153+2</f>
         <v/>
       </c>
-      <c r="G154" s="47" t="n"/>
-      <c r="H154" s="47" t="n"/>
-      <c r="I154" s="47" t="n"/>
-      <c r="J154" s="47">
+      <c r="G154" s="49" t="n"/>
+      <c r="H154" s="49" t="n"/>
+      <c r="I154" s="49" t="n"/>
+      <c r="J154" s="49">
         <f>IF(OR(NOT(ISNUMBER(E154)),NOT(ISNUMBER(I154))),"NULL",E154-I154)</f>
         <v/>
       </c>
@@ -3525,17 +3527,17 @@
         <f>B154+2</f>
         <v/>
       </c>
-      <c r="C155" s="47" t="n"/>
-      <c r="D155" s="47" t="n"/>
-      <c r="E155" s="47" t="n"/>
+      <c r="C155" s="49" t="n"/>
+      <c r="D155" s="49" t="n"/>
+      <c r="E155" s="49" t="n"/>
       <c r="F155" s="32">
         <f>F154+2</f>
         <v/>
       </c>
-      <c r="G155" s="47" t="n"/>
-      <c r="H155" s="47" t="n"/>
-      <c r="I155" s="47" t="n"/>
-      <c r="J155" s="47">
+      <c r="G155" s="49" t="n"/>
+      <c r="H155" s="49" t="n"/>
+      <c r="I155" s="49" t="n"/>
+      <c r="J155" s="49">
         <f>IF(OR(NOT(ISNUMBER(E155)),NOT(ISNUMBER(I155))),"NULL",E155-I155)</f>
         <v/>
       </c>
@@ -3547,17 +3549,17 @@
         <f>B155+2</f>
         <v/>
       </c>
-      <c r="C156" s="47" t="n"/>
-      <c r="D156" s="47" t="n"/>
-      <c r="E156" s="47" t="n"/>
+      <c r="C156" s="49" t="n"/>
+      <c r="D156" s="49" t="n"/>
+      <c r="E156" s="49" t="n"/>
       <c r="F156" s="32">
         <f>F155+2</f>
         <v/>
       </c>
-      <c r="G156" s="47" t="n"/>
-      <c r="H156" s="47" t="n"/>
-      <c r="I156" s="47" t="n"/>
-      <c r="J156" s="47">
+      <c r="G156" s="49" t="n"/>
+      <c r="H156" s="49" t="n"/>
+      <c r="I156" s="49" t="n"/>
+      <c r="J156" s="49">
         <f>IF(OR(NOT(ISNUMBER(E156)),NOT(ISNUMBER(I156))),"NULL",E156-I156)</f>
         <v/>
       </c>
@@ -3569,17 +3571,17 @@
         <f>B156+2</f>
         <v/>
       </c>
-      <c r="C157" s="47" t="n"/>
-      <c r="D157" s="47" t="n"/>
-      <c r="E157" s="47" t="n"/>
+      <c r="C157" s="49" t="n"/>
+      <c r="D157" s="49" t="n"/>
+      <c r="E157" s="49" t="n"/>
       <c r="F157" s="32">
         <f>F156+2</f>
         <v/>
       </c>
-      <c r="G157" s="47" t="n"/>
-      <c r="H157" s="47" t="n"/>
-      <c r="I157" s="47" t="n"/>
-      <c r="J157" s="47">
+      <c r="G157" s="49" t="n"/>
+      <c r="H157" s="49" t="n"/>
+      <c r="I157" s="49" t="n"/>
+      <c r="J157" s="49">
         <f>IF(OR(NOT(ISNUMBER(E157)),NOT(ISNUMBER(I157))),"NULL",E157-I157)</f>
         <v/>
       </c>
@@ -3591,17 +3593,17 @@
         <f>B157+2</f>
         <v/>
       </c>
-      <c r="C158" s="47" t="n"/>
-      <c r="D158" s="47" t="n"/>
-      <c r="E158" s="47" t="n"/>
+      <c r="C158" s="49" t="n"/>
+      <c r="D158" s="49" t="n"/>
+      <c r="E158" s="49" t="n"/>
       <c r="F158" s="32">
         <f>F157+2</f>
         <v/>
       </c>
-      <c r="G158" s="47" t="n"/>
-      <c r="H158" s="47" t="n"/>
-      <c r="I158" s="47" t="n"/>
-      <c r="J158" s="47">
+      <c r="G158" s="49" t="n"/>
+      <c r="H158" s="49" t="n"/>
+      <c r="I158" s="49" t="n"/>
+      <c r="J158" s="49">
         <f>IF(OR(NOT(ISNUMBER(E158)),NOT(ISNUMBER(I158))),"NULL",E158-I158)</f>
         <v/>
       </c>
@@ -3613,17 +3615,17 @@
         <f>B158+2</f>
         <v/>
       </c>
-      <c r="C159" s="47" t="n"/>
-      <c r="D159" s="47" t="n"/>
-      <c r="E159" s="47" t="n"/>
+      <c r="C159" s="49" t="n"/>
+      <c r="D159" s="49" t="n"/>
+      <c r="E159" s="49" t="n"/>
       <c r="F159" s="32">
         <f>F158+2</f>
         <v/>
       </c>
-      <c r="G159" s="47" t="n"/>
-      <c r="H159" s="47" t="n"/>
-      <c r="I159" s="47" t="n"/>
-      <c r="J159" s="47">
+      <c r="G159" s="49" t="n"/>
+      <c r="H159" s="49" t="n"/>
+      <c r="I159" s="49" t="n"/>
+      <c r="J159" s="49">
         <f>IF(OR(NOT(ISNUMBER(E159)),NOT(ISNUMBER(I159))),"NULL",E159-I159)</f>
         <v/>
       </c>
@@ -3635,17 +3637,17 @@
         <f>B159+2</f>
         <v/>
       </c>
-      <c r="C160" s="47" t="n"/>
-      <c r="D160" s="47" t="n"/>
-      <c r="E160" s="47" t="n"/>
+      <c r="C160" s="49" t="n"/>
+      <c r="D160" s="49" t="n"/>
+      <c r="E160" s="49" t="n"/>
       <c r="F160" s="32">
         <f>F159+2</f>
         <v/>
       </c>
-      <c r="G160" s="47" t="n"/>
-      <c r="H160" s="47" t="n"/>
-      <c r="I160" s="47" t="n"/>
-      <c r="J160" s="47">
+      <c r="G160" s="49" t="n"/>
+      <c r="H160" s="49" t="n"/>
+      <c r="I160" s="49" t="n"/>
+      <c r="J160" s="49">
         <f>IF(OR(NOT(ISNUMBER(E160)),NOT(ISNUMBER(I160))),"NULL",E160-I160)</f>
         <v/>
       </c>
@@ -3657,17 +3659,17 @@
         <f>B160+2</f>
         <v/>
       </c>
-      <c r="C161" s="47" t="n"/>
-      <c r="D161" s="47" t="n"/>
-      <c r="E161" s="47" t="n"/>
+      <c r="C161" s="49" t="n"/>
+      <c r="D161" s="49" t="n"/>
+      <c r="E161" s="49" t="n"/>
       <c r="F161" s="32">
         <f>F160+2</f>
         <v/>
       </c>
-      <c r="G161" s="47" t="n"/>
-      <c r="H161" s="47" t="n"/>
-      <c r="I161" s="47" t="n"/>
-      <c r="J161" s="47">
+      <c r="G161" s="49" t="n"/>
+      <c r="H161" s="49" t="n"/>
+      <c r="I161" s="49" t="n"/>
+      <c r="J161" s="49">
         <f>IF(OR(NOT(ISNUMBER(E161)),NOT(ISNUMBER(I161))),"NULL",E161-I161)</f>
         <v/>
       </c>
@@ -3679,17 +3681,17 @@
         <f>B161+2</f>
         <v/>
       </c>
-      <c r="C162" s="47" t="n"/>
-      <c r="D162" s="47" t="n"/>
-      <c r="E162" s="47" t="n"/>
+      <c r="C162" s="49" t="n"/>
+      <c r="D162" s="49" t="n"/>
+      <c r="E162" s="49" t="n"/>
       <c r="F162" s="32">
         <f>F161+2</f>
         <v/>
       </c>
-      <c r="G162" s="47" t="n"/>
-      <c r="H162" s="47" t="n"/>
-      <c r="I162" s="47" t="n"/>
-      <c r="J162" s="47">
+      <c r="G162" s="49" t="n"/>
+      <c r="H162" s="49" t="n"/>
+      <c r="I162" s="49" t="n"/>
+      <c r="J162" s="49">
         <f>IF(OR(NOT(ISNUMBER(E162)),NOT(ISNUMBER(I162))),"NULL",E162-I162)</f>
         <v/>
       </c>
@@ -3838,9 +3840,9 @@
           <t>RMP-A</t>
         </is>
       </c>
-      <c r="C4" s="48" t="n"/>
-      <c r="D4" s="48" t="n"/>
-      <c r="E4" s="48" t="n"/>
+      <c r="C4" s="50" t="n"/>
+      <c r="D4" s="50" t="n"/>
+      <c r="E4" s="50" t="n"/>
     </row>
     <row r="5">
       <c r="B5" s="46" t="inlineStr">
@@ -3848,9 +3850,9 @@
           <t>RMP-B</t>
         </is>
       </c>
-      <c r="C5" s="48" t="n"/>
-      <c r="D5" s="48" t="n"/>
-      <c r="E5" s="48" t="n"/>
+      <c r="C5" s="50" t="n"/>
+      <c r="D5" s="50" t="n"/>
+      <c r="E5" s="50" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="46" t="inlineStr">
@@ -3858,9 +3860,9 @@
           <t>RMP-C</t>
         </is>
       </c>
-      <c r="C6" s="48" t="n"/>
-      <c r="D6" s="48" t="n"/>
-      <c r="E6" s="48" t="n"/>
+      <c r="C6" s="50" t="n"/>
+      <c r="D6" s="50" t="n"/>
+      <c r="E6" s="50" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/TRACK_MONITORING_REPORT.xlsx
+++ b/TRACK_MONITORING_REPORT.xlsx
@@ -21,7 +21,7 @@
     <numFmt numFmtId="165" formatCode="mm\-dd\-yy"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="19">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -108,6 +108,18 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -277,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -381,6 +393,11 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3796,13 +3813,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E6"/>
+  <dimension ref="B1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3813,58 +3835,165 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="45" t="inlineStr">
+      <c r="B3" s="44" t="inlineStr">
+        <is>
+          <t>LANDMARK SURVEYS L.L.C.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LS File: </t>
+        </is>
+      </c>
+      <c r="I3" s="51" t="inlineStr">
+        <is>
+          <t>25146</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>51 BRIDGE STREET</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date of Field Observation: </t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>METUCHEN, NEW JERSEY  08840</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time of Field Observation: </t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TEL#  (732) 548-8782</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sheet: </t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">of </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="H7" s="52" t="inlineStr">
+        <is>
+          <t>Cert. of Auth. #24GA2872300</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PROJECT:</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>STAFFORD ROAD SANITARY SEWER PHASE I</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CONTRACTOR:</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MONTANA CONSTRUCTION</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>REV 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="53" t="inlineStr">
         <is>
           <t>Point Name</t>
         </is>
       </c>
-      <c r="C3" s="45" t="inlineStr">
+      <c r="C11" s="53" t="inlineStr">
         <is>
           <t>Delta Northing (DN)</t>
         </is>
       </c>
-      <c r="D3" s="45" t="inlineStr">
+      <c r="D11" s="53" t="inlineStr">
         <is>
           <t>Delta Easting (DE)</t>
         </is>
       </c>
-      <c r="E3" s="45" t="inlineStr">
+      <c r="E11" s="53" t="inlineStr">
         <is>
           <t>Delta Elevation (DELV)</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="46" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="46" t="inlineStr">
         <is>
           <t>RMP-A</t>
         </is>
       </c>
-      <c r="C4" s="50" t="n"/>
-      <c r="D4" s="50" t="n"/>
-      <c r="E4" s="50" t="n"/>
-    </row>
-    <row r="5">
-      <c r="B5" s="46" t="inlineStr">
+      <c r="C12" s="50" t="n"/>
+      <c r="D12" s="50" t="n"/>
+      <c r="E12" s="50" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="46" t="inlineStr">
         <is>
           <t>RMP-B</t>
         </is>
       </c>
-      <c r="C5" s="50" t="n"/>
-      <c r="D5" s="50" t="n"/>
-      <c r="E5" s="50" t="n"/>
-    </row>
-    <row r="6">
-      <c r="B6" s="46" t="inlineStr">
+      <c r="C13" s="50" t="n"/>
+      <c r="D13" s="50" t="n"/>
+      <c r="E13" s="50" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="46" t="inlineStr">
         <is>
           <t>RMP-C</t>
         </is>
       </c>
-      <c r="C6" s="50" t="n"/>
-      <c r="D6" s="50" t="n"/>
-      <c r="E6" s="50" t="n"/>
+      <c r="C14" s="50" t="n"/>
+      <c r="D14" s="50" t="n"/>
+      <c r="E14" s="50" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I3:J3"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>